--- a/docs/excel/flow_mock_excel.xlsx
+++ b/docs/excel/flow_mock_excel.xlsx
@@ -2085,8 +2085,8 @@
       <c r="E4" s="15" t="inlineStr">
         <is>
           <t>{
-"email": "string",
-"otp_code": "string: 6 digits"
+  "email": "user@example.com",
+  "otp": "123456"
 }</t>
         </is>
       </c>
@@ -2459,10 +2459,10 @@
       <c r="E9" s="10" t="inlineStr">
         <is>
           <t>{
-"email": "string",
-"otp_code": "string: 6 digits",
-"new_password": "string",
-"confirm_password": "string"
+  "email": "user@example.com",
+  "otpCode": "123456",
+  "newPassword": "NewPassword123@",
+  "confirmPassword": "NewPassword123@"
 }</t>
         </is>
       </c>
@@ -2969,19 +2969,19 @@
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Body:
 {
-"username": "string (optional, max 100)",
-"first_name": "string",
-"last_name": "string",
-"phone_number": "string",
-"address": {
-"province_id": "int",
-"district_id": "int",
-"ward_code": "string",
-"street_address": "string"
-}
+  "username": "string (optional, max 100)",
+  "firstName": "string",
+  "lastName": "string",
+  "phoneNumber": "string",
+  "address": {
+    "provinceId": 1,
+    "districtId": 1,
+    "wardCode": "001",
+    "streetAddress": "string"
+  }
 }</t>
         </is>
       </c>
@@ -3940,15 +3940,15 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Body:
 {
-"transaction_type": "string (\"ORDER\" | \"AUCTION\")",
-"transaction_id": "uuid",
-"target_user_id": "uuid",
-"rating": "int (1..5)",
-"comment": "string (10..500 ký tự)",
-"media_urls": "string[] (optional)"
+  "transactionType": "ORDER|AUCTION",
+  "transactionId": "uuid",
+  "targetUserId": "uuid",
+  "rating": 5,
+  "comment": "Giao hang nhanh, dong goi can than.",
+  "mediaUrls": ["https://img.example.com/review1.png"]
 }</t>
         </is>
       </c>
@@ -4119,13 +4119,13 @@
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Body:
 {
-"reported_user_id": "uuid",
-"violation_type": "string",
-"description": "string (10..1000 ký tự)",
-"evidence_urls": "string[] (optional)"
+  "reportedUserId": "uuid",
+  "violationType": "SPAM|FRAUD|INAPPROPRIATE_CONTENT",
+  "description": "Nguoi dung co hanh vi gian lan.",
+  "evidenceUrls": ["https://img.example.com/evidence1.png"]
 }</t>
         </is>
       </c>
@@ -4286,19 +4286,19 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Body:
 {
-"shopName": "string",
-"businessEmail": "string",
-"hotline": "string",
-"warehouseAddress": {
-"province_id": "int",
-"district_id": "int",
-"ward_code": "string",
-"street_address": "string"
-},
-"identityCardNumber": "string"
+  "shopName": "string",
+  "businessEmail": "string",
+  "hotline": "string",
+  "warehouseAddress": {
+    "provinceId": 1,
+    "districtId": 1,
+    "wardCode": "001",
+    "streetAddress": "string"
+  },
+  "identityCardNumber": "string"
 }</t>
         </is>
       </c>
@@ -4752,18 +4752,18 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Body:
 {
-"shopName": "string (optional)",
-"hotline": "string (optional)",
-"pickupAddress": {
-"province_id": "int",
-"district_id": "int",
-"ward_code": "string",
-"street_address": "string"
-},
-"description": "string"
+  "shopName": "string",
+  "hotline": "string",
+  "pickupAddress": {
+    "provinceId": 1,
+    "districtId": 1,
+    "wardCode": "001",
+    "streetAddress": "string"
+  },
+  "description": "string"
 }</t>
         </is>
       </c>
@@ -5183,13 +5183,13 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Query:
 {
-"page": "int (default: 1)",
-"limit": "int (default: 20)",
-"status": "string (optional)",
-"violation_type": "string (optional)"
+  "page": 1,
+  "limit": 20,
+  "status": "PENDING|RESOLVED|DISMISSED",
+  "violationType": "SPAM|FRAUD"
 }</t>
         </is>
       </c>
@@ -6186,17 +6186,13 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Path: { "userId": "uuid" }
 Body:
 {
-"role_codes": [
-"STAFF"
-],
-"role_ids": [
-1
-],
-"reason": "string"
+  "roleCodes": ["Staff"],
+  "roleIds": [1],
+  "reason": "Promotion to customer support staff."
 }</t>
         </is>
       </c>
@@ -6505,12 +6501,12 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
-Path: { "roleId": "int" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
+Path: { "roleId": 1 }
 Body:
 {
-"description": "string",
-"permission_ids": "int[]"
+  "description": "Customer support and complaint resolution.",
+  "permissionIds": [1, 2, 3]
 }</t>
         </is>
       </c>
@@ -6579,44 +6575,45 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Headers: { "Authorization": "Bearer JWT" }
+          <t>Headers: { "Authorization": "Bearer &lt;JWT&gt;" }
 Query:
 {
-"page": "int (default: 1)",
-"limit": "int (default: 20)",
-"actor_id": "uuid (optional)",
-"action": "string (optional)",
-"from_date": "datetime (optional)",
-"to_date": "datetime (optional)"
+  "page": 1,
+  "limit": 20,
+  "actorId": "uuid",
+  "action": "string",
+  "fromDate": "2026-10-01T00:00:00Z",
+  "toDate": "2026-10-26T00:00:00Z"
 }</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>{
-"msg": "Lấy nhật ký kiểm toán thành công",
-"data": {
-"items": [
+          <t>200 OK:
 {
-"id": "uuid",
-"actorId": "uuid",
-"action": "string",
-"targetEntity": "string",
-"oldValues": "object",
-"newValues": "object",
-"reason": "string",
-"ipAddress": "string",
-"createdAt": "timestamp"
-}
-]
-}
+  "items": [
+    {
+      "id": "uuid",
+      "actorId": "uuid",
+      "action": "USER_BANNED",
+      "targetEntity": "users",
+      "oldValues": {},
+      "newValues": {},
+      "reason": "Policy violation.",
+      "ipAddress": "127.0.0.1",
+      "createdAt": "2026-10-26T00:00:00Z"
+    }
+  ],
+  "total": 1,
+  "page": 1,
+  "limit": 20
 }</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>- [401] ERR_UNAUTHORIZED: Chưa đăng nhập
-- [403] ERR_PERMISSION_DENIED: Không có quyền tra cứu nhật ký kiểm toán (audit:view)</t>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have permission to view audit logs.</t>
         </is>
       </c>
       <c r="H60" s="84" t="n"/>
@@ -6999,7 +6996,11 @@
 }</t>
         </is>
       </c>
-      <c r="G66" s="18" t="n"/>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_PAGE: Page and pageSize must be positive integers.</t>
+        </is>
+      </c>
       <c r="H66" s="30" t="n"/>
       <c r="I66" s="8" t="inlineStr">
         <is>
@@ -7082,7 +7083,11 @@
 }</t>
         </is>
       </c>
-      <c r="G67" s="34" t="n"/>
+      <c r="G67" s="34" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_FILTER: Search filter parameters are invalid.</t>
+        </is>
+      </c>
       <c r="H67" s="30" t="n"/>
       <c r="I67" s="32" t="inlineStr">
         <is>
@@ -7178,7 +7183,12 @@
 }</t>
         </is>
       </c>
-      <c r="G68" s="18" t="n"/>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_PRODUCT_ID: Product ID format is invalid.
+404 PRODUCT_NOT_FOUND: Product was not found or is inactive.</t>
+        </is>
+      </c>
       <c r="H68" s="30" t="n"/>
       <c r="I68" s="8" t="inlineStr">
         <is>
@@ -15353,13 +15363,57 @@
     </row>
     <row r="185" ht="15.75" customHeight="1" s="81">
       <c r="A185" s="9" t="n"/>
-      <c r="B185" s="9" t="n"/>
-      <c r="C185" s="21" t="n"/>
-      <c r="D185" s="21" t="n"/>
-      <c r="E185" s="21" t="n"/>
-      <c r="F185" s="21" t="n"/>
-      <c r="G185" s="21" t="n"/>
-      <c r="H185" s="66" t="n"/>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C185" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/devices</t>
+        </is>
+      </c>
+      <c r="D185" s="21" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc làm mới FCM/APNs device token để nhận push notification</t>
+        </is>
+      </c>
+      <c r="E185" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Body:
+{
+  "platform": "WEB|IOS|ANDROID",
+  "token": "string"
+}</t>
+        </is>
+      </c>
+      <c r="F185" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "deviceId": "uuid",
+  "userId": "uuid",
+  "platform": "WEB|IOS|ANDROID",
+  "isActive": true,
+  "lastSeenAt": "2026-10-26T00:00:00Z"
+}</t>
+        </is>
+      </c>
+      <c r="G185" s="21" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_DEVICE_TOKEN: Platform or token is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.</t>
+        </is>
+      </c>
+      <c r="H185" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-01</t>
+        </is>
+      </c>
       <c r="I185" s="21" t="n"/>
       <c r="J185" s="21" t="n"/>
       <c r="K185" s="21" t="n"/>
@@ -15382,13 +15436,50 @@
     </row>
     <row r="186" ht="15.75" customHeight="1" s="81">
       <c r="A186" s="76" t="n"/>
-      <c r="B186" s="76" t="n"/>
-      <c r="C186" s="77" t="n"/>
-      <c r="D186" s="77" t="n"/>
-      <c r="E186" s="77" t="n"/>
-      <c r="F186" s="77" t="n"/>
-      <c r="G186" s="77" t="n"/>
-      <c r="H186" s="66" t="n"/>
+      <c r="B186" s="76" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="C186" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/devices</t>
+        </is>
+      </c>
+      <c r="D186" s="77" t="inlineStr">
+        <is>
+          <t>Thu hồi hoặc vô hiệu hóa device token khi logout hoặc tắt quyền push</t>
+        </is>
+      </c>
+      <c r="E186" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Body:
+{
+  "token": "string"
+}</t>
+        </is>
+      </c>
+      <c r="F186" s="77" t="inlineStr">
+        <is>
+          <t>204 No Content</t>
+        </is>
+      </c>
+      <c r="G186" s="77" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_TOKEN: Token is missing or invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+404 DEVICE_TOKEN_NOT_FOUND: Device token was not found for this user.</t>
+        </is>
+      </c>
+      <c r="H186" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-02</t>
+        </is>
+      </c>
       <c r="I186" s="77" t="n"/>
       <c r="J186" s="77" t="n"/>
       <c r="K186" s="77" t="n"/>
@@ -15411,13 +15502,54 @@
     </row>
     <row r="187" ht="15.75" customHeight="1" s="81">
       <c r="A187" s="9" t="n"/>
-      <c r="B187" s="9" t="n"/>
-      <c r="C187" s="21" t="n"/>
-      <c r="D187" s="21" t="n"/>
-      <c r="E187" s="21" t="n"/>
-      <c r="F187" s="21" t="n"/>
-      <c r="G187" s="21" t="n"/>
-      <c r="H187" s="66" t="n"/>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C187" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/preferences</t>
+        </is>
+      </c>
+      <c r="D187" s="21" t="inlineStr">
+        <is>
+          <t>Lấy danh sách cấu hình bật/tắt nhận thông báo của người dùng</t>
+        </is>
+      </c>
+      <c r="E187" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "items": [
+    {
+      "notificationType": "ORDER_PAID|AUCTION_OUTBID|PROMOTION",
+      "channelCode": "EMAIL|PUSH|IN_APP",
+      "isEnabled": true,
+      "isMandatory": true
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G187" s="21" t="inlineStr">
+        <is>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.</t>
+        </is>
+      </c>
+      <c r="H187" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-03</t>
+        </is>
+      </c>
       <c r="I187" s="21" t="n"/>
       <c r="J187" s="21" t="n"/>
       <c r="K187" s="21" t="n"/>
@@ -15440,13 +15572,66 @@
     </row>
     <row r="188" ht="15.75" customHeight="1" s="81">
       <c r="A188" s="76" t="n"/>
-      <c r="B188" s="76" t="n"/>
-      <c r="C188" s="77" t="n"/>
-      <c r="D188" s="77" t="n"/>
-      <c r="E188" s="77" t="n"/>
-      <c r="F188" s="77" t="n"/>
-      <c r="G188" s="77" t="n"/>
-      <c r="H188" s="66" t="n"/>
+      <c r="B188" s="76" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C188" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/preferences</t>
+        </is>
+      </c>
+      <c r="D188" s="77" t="inlineStr">
+        <is>
+          <t>Cập nhật tùy chọn bật/tắt nhận thông báo theo loại sự kiện và kênh gửi</t>
+        </is>
+      </c>
+      <c r="E188" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Body:
+{
+  "preferences": [
+    {
+      "notificationType": "ORDER_PAID",
+      "channelCode": "EMAIL",
+      "isEnabled": true
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="F188" s="77" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "updatedCount": 1,
+  "preferences": [
+    {
+      "notificationType": "ORDER_PAID",
+      "channelCode": "EMAIL",
+      "isEnabled": true
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G188" s="77" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_PREFERENCES: Notification type or channel code is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+422 MANDATORY_NOTIFICATION_CANNOT_DISABLE: Mandatory security or transaction notification cannot be disabled.</t>
+        </is>
+      </c>
+      <c r="H188" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-04</t>
+        </is>
+      </c>
       <c r="I188" s="77" t="n"/>
       <c r="J188" s="77" t="n"/>
       <c r="K188" s="77" t="n"/>
@@ -15469,13 +15654,71 @@
     </row>
     <row r="189" ht="15.75" customHeight="1" s="81">
       <c r="A189" s="9" t="n"/>
-      <c r="B189" s="9" t="n"/>
-      <c r="C189" s="21" t="n"/>
-      <c r="D189" s="21" t="n"/>
-      <c r="E189" s="21" t="n"/>
-      <c r="F189" s="21" t="n"/>
-      <c r="G189" s="21" t="n"/>
-      <c r="H189" s="66" t="n"/>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C189" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/me</t>
+        </is>
+      </c>
+      <c r="D189" s="21" t="inlineStr">
+        <is>
+          <t>Lấy danh sách lịch sử thông báo in-app (quả chuông) kèm số lượng chưa đọc</t>
+        </is>
+      </c>
+      <c r="E189" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Query:
+{
+  "isRead": false,
+  "notificationType": "ORDER_PAID",
+  "pageIndex": 1,
+  "pageSize": 20
+}</t>
+        </is>
+      </c>
+      <c r="F189" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "unreadCount": 3,
+  "totalCount": 10,
+  "items": [
+    {
+      "id": "uuid",
+      "notificationType": "ORDER_PAID",
+      "title": "Don hang #SUB-01 da duoc thanh toan",
+      "body": "Don hang tri gia 480.000d da duoc thanh toan thanh cong.",
+      "payload": {
+        "orderId": "uuid",
+        "subOrderId": "uuid"
+      },
+      "isRead": false,
+      "readAt": null,
+      "createdAt": "2026-10-26T00:00:00Z"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G189" s="21" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_PAGE: PageIndex or pageSize is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.</t>
+        </is>
+      </c>
+      <c r="H189" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-05</t>
+        </is>
+      </c>
       <c r="I189" s="21" t="n"/>
       <c r="J189" s="21" t="n"/>
       <c r="K189" s="21" t="n"/>
@@ -15498,13 +15741,54 @@
     </row>
     <row r="190" ht="15.75" customHeight="1" s="81">
       <c r="A190" s="76" t="n"/>
-      <c r="B190" s="76" t="n"/>
-      <c r="C190" s="77" t="n"/>
-      <c r="D190" s="77" t="n"/>
-      <c r="E190" s="77" t="n"/>
-      <c r="F190" s="77" t="n"/>
-      <c r="G190" s="77" t="n"/>
-      <c r="H190" s="66" t="n"/>
+      <c r="B190" s="76" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="C190" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/notifications/me/read</t>
+        </is>
+      </c>
+      <c r="D190" s="77" t="inlineStr">
+        <is>
+          <t>Đánh dấu một số hoặc toàn bộ thông báo trong hộp thư là đã đọc</t>
+        </is>
+      </c>
+      <c r="E190" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Body:
+{
+  "notificationIds": ["uuid"],
+  "markAll": false
+}</t>
+        </is>
+      </c>
+      <c r="F190" s="77" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "updatedCount": 1,
+  "unreadCount": 2
+}</t>
+        </is>
+      </c>
+      <c r="G190" s="77" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_INPUT: Notification IDs list is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.</t>
+        </is>
+      </c>
+      <c r="H190" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-06</t>
+        </is>
+      </c>
       <c r="I190" s="77" t="n"/>
       <c r="J190" s="77" t="n"/>
       <c r="K190" s="77" t="n"/>
@@ -15527,13 +15811,63 @@
     </row>
     <row r="191" ht="15.75" customHeight="1" s="81">
       <c r="A191" s="9" t="n"/>
-      <c r="B191" s="9" t="n"/>
-      <c r="C191" s="21" t="n"/>
-      <c r="D191" s="21" t="n"/>
-      <c r="E191" s="21" t="n"/>
-      <c r="F191" s="21" t="n"/>
-      <c r="G191" s="21" t="n"/>
-      <c r="H191" s="66" t="n"/>
+      <c r="B191" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C191" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/notifications/channels/{code}</t>
+        </is>
+      </c>
+      <c r="D191" s="21" t="inlineStr">
+        <is>
+          <t>Admin xem trạng thái và cấu hình kênh gửi thông báo</t>
+        </is>
+      </c>
+      <c r="E191" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Path:
+{
+  "code": "EMAIL|PUSH|IN_APP|SMS"
+}</t>
+        </is>
+      </c>
+      <c r="F191" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "id": "uuid",
+  "code": "EMAIL",
+  "name": "Email Service",
+  "provider": "SMTP",
+  "config": {
+    "host": "smtp.example.com",
+    "port": 587,
+    "fromAddress": "noreply@shop.example.com"
+  },
+  "isEnabled": true,
+  "updatedAt": "2026-10-26T00:00:00Z"
+}</t>
+        </is>
+      </c>
+      <c r="G191" s="21" t="inlineStr">
+        <is>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.
+404 CHANNEL_NOT_FOUND: Notification channel code was not found.</t>
+        </is>
+      </c>
+      <c r="H191" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-07</t>
+        </is>
+      </c>
       <c r="I191" s="21" t="n"/>
       <c r="J191" s="21" t="n"/>
       <c r="K191" s="21" t="n"/>
@@ -15556,13 +15890,75 @@
     </row>
     <row r="192" ht="15.75" customHeight="1" s="81">
       <c r="A192" s="76" t="n"/>
-      <c r="B192" s="76" t="n"/>
-      <c r="C192" s="77" t="n"/>
-      <c r="D192" s="77" t="n"/>
-      <c r="E192" s="77" t="n"/>
-      <c r="F192" s="77" t="n"/>
-      <c r="G192" s="77" t="n"/>
-      <c r="H192" s="66" t="n"/>
+      <c r="B192" s="76" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="C192" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/notifications/channels/{code}</t>
+        </is>
+      </c>
+      <c r="D192" s="77" t="inlineStr">
+        <is>
+          <t>Admin cập nhật cấu hình và bật/tắt kênh gửi thông báo</t>
+        </is>
+      </c>
+      <c r="E192" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Path:
+{
+  "code": "EMAIL|PUSH|IN_APP|SMS"
+}
+Body:
+{
+  "name": "Email Service",
+  "provider": "SMTP",
+  "config": {
+    "host": "smtp.example.com",
+    "port": 587,
+    "fromAddress": "noreply@shop.example.com"
+  },
+  "isEnabled": true
+}</t>
+        </is>
+      </c>
+      <c r="F192" s="77" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "id": "uuid",
+  "code": "EMAIL",
+  "name": "Email Service",
+  "provider": "SMTP",
+  "config": {
+    "host": "smtp.example.com",
+    "port": 587,
+    "fromAddress": "noreply@shop.example.com"
+  },
+  "isEnabled": true,
+  "updatedAt": "2026-10-26T00:00:00Z"
+}</t>
+        </is>
+      </c>
+      <c r="G192" s="77" t="inlineStr">
+        <is>
+          <t>400 SECRET_IN_CONFIG_FORBIDDEN: Secrets like passwords or API keys are not allowed in config body.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.
+404 CHANNEL_NOT_FOUND: Notification channel code was not found.</t>
+        </is>
+      </c>
+      <c r="H192" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-07</t>
+        </is>
+      </c>
       <c r="I192" s="77" t="n"/>
       <c r="J192" s="77" t="n"/>
       <c r="K192" s="77" t="n"/>
@@ -15585,13 +15981,65 @@
     </row>
     <row r="193" ht="15.75" customHeight="1" s="81">
       <c r="A193" s="9" t="n"/>
-      <c r="B193" s="9" t="n"/>
-      <c r="C193" s="21" t="n"/>
-      <c r="D193" s="21" t="n"/>
-      <c r="E193" s="21" t="n"/>
-      <c r="F193" s="21" t="n"/>
-      <c r="G193" s="21" t="n"/>
-      <c r="H193" s="66" t="n"/>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C193" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/notifications/templates</t>
+        </is>
+      </c>
+      <c r="D193" s="21" t="inlineStr">
+        <is>
+          <t>Admin xem danh sách mẫu thông báo (Template Engine)</t>
+        </is>
+      </c>
+      <c r="E193" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Query:
+{
+  "channelCode": "EMAIL",
+  "notificationType": "ORDER_PAID"
+}</t>
+        </is>
+      </c>
+      <c r="F193" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "items": [
+    {
+      "id": "uuid",
+      "code": "ORDER_PAID_EMAIL",
+      "notificationType": "ORDER_PAID",
+      "channelCode": "EMAIL",
+      "subjectTemplate": "Don hang {{orderNo}} thanh toan thanh cong",
+      "bodyTemplate": "&lt;p&gt;Xin chao {{userName}}, don hang {{orderNo}} da duoc xac nhan.&lt;/p&gt;",
+      "isMandatory": true,
+      "locale": "vi-VN",
+      "isActive": true
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G193" s="21" t="inlineStr">
+        <is>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.</t>
+        </is>
+      </c>
+      <c r="H193" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-08</t>
+        </is>
+      </c>
       <c r="I193" s="21" t="n"/>
       <c r="J193" s="21" t="n"/>
       <c r="K193" s="21" t="n"/>
@@ -15614,13 +16062,67 @@
     </row>
     <row r="194" ht="15.75" customHeight="1" s="81">
       <c r="A194" s="76" t="n"/>
-      <c r="B194" s="76" t="n"/>
-      <c r="C194" s="77" t="n"/>
-      <c r="D194" s="77" t="n"/>
-      <c r="E194" s="77" t="n"/>
-      <c r="F194" s="77" t="n"/>
-      <c r="G194" s="77" t="n"/>
-      <c r="H194" s="66" t="n"/>
+      <c r="B194" s="76" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C194" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/notifications/templates</t>
+        </is>
+      </c>
+      <c r="D194" s="77" t="inlineStr">
+        <is>
+          <t>Admin tạo mẫu nội dung thông báo mới</t>
+        </is>
+      </c>
+      <c r="E194" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Body:
+{
+  "code": "ORDER_PAID_EMAIL",
+  "notificationType": "ORDER_PAID",
+  "channelCode": "EMAIL",
+  "subjectTemplate": "Don hang {{orderNo}} thanh toan thanh cong",
+  "bodyTemplate": "&lt;p&gt;Xin chao {{userName}}, don hang {{orderNo}} da duoc xac nhan.&lt;/p&gt;",
+  "isMandatory": true,
+  "locale": "vi-VN",
+  "isActive": true
+}</t>
+        </is>
+      </c>
+      <c r="F194" s="77" t="inlineStr">
+        <is>
+          <t>201 Created:
+{
+  "id": "uuid",
+  "code": "ORDER_PAID_EMAIL",
+  "notificationType": "ORDER_PAID",
+  "channelCode": "EMAIL",
+  "isMandatory": true,
+  "locale": "vi-VN",
+  "isActive": true
+}</t>
+        </is>
+      </c>
+      <c r="G194" s="77" t="inlineStr">
+        <is>
+          <t>400 INVALID_TEMPLATE_SYNTAX: Template syntax is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.
+409 TEMPLATE_CODE_DUPLICATED: Template code and locale already exist.</t>
+        </is>
+      </c>
+      <c r="H194" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-08</t>
+        </is>
+      </c>
       <c r="I194" s="77" t="n"/>
       <c r="J194" s="77" t="n"/>
       <c r="K194" s="77" t="n"/>
@@ -15643,13 +16145,75 @@
     </row>
     <row r="195" ht="15.75" customHeight="1" s="81">
       <c r="A195" s="9" t="n"/>
-      <c r="B195" s="9" t="n"/>
-      <c r="C195" s="21" t="n"/>
-      <c r="D195" s="21" t="n"/>
-      <c r="E195" s="21" t="n"/>
-      <c r="F195" s="21" t="n"/>
-      <c r="G195" s="21" t="n"/>
-      <c r="H195" s="66" t="n"/>
+      <c r="B195" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C195" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/notifications</t>
+        </is>
+      </c>
+      <c r="D195" s="21" t="inlineStr">
+        <is>
+          <t>Admin/Staff tra cứu lịch sử gửi thông báo và nhật ký lỗi delivery</t>
+        </is>
+      </c>
+      <c r="E195" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Query:
+{
+  "userId": "uuid",
+  "notificationType": "ORDER_PAID",
+  "status": "COMPLETED|PENDING|FAILED",
+  "pageIndex": 1,
+  "pageSize": 20
+}</t>
+        </is>
+      </c>
+      <c r="F195" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "total": 1,
+  "items": [
+    {
+      "notificationId": "uuid",
+      "userId": "uuid",
+      "notificationType": "ORDER_PAID",
+      "status": "COMPLETED",
+      "createdAt": "2026-10-26T00:00:00Z",
+      "deliveries": [
+        {
+          "deliveryId": "uuid",
+          "channelCode": "EMAIL",
+          "destination": "u***@gmail.com",
+          "status": "SENT",
+          "attemptCount": 1
+        }
+      ]
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G195" s="21" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_FILTER: Query filter parameters are invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.</t>
+        </is>
+      </c>
+      <c r="H195" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-09</t>
+        </is>
+      </c>
       <c r="I195" s="21" t="n"/>
       <c r="J195" s="21" t="n"/>
       <c r="K195" s="21" t="n"/>
@@ -15672,13 +16236,66 @@
     </row>
     <row r="196" ht="15.75" customHeight="1" s="81">
       <c r="A196" s="76" t="n"/>
-      <c r="B196" s="76" t="n"/>
-      <c r="C196" s="77" t="n"/>
-      <c r="D196" s="77" t="n"/>
-      <c r="E196" s="77" t="n"/>
-      <c r="F196" s="77" t="n"/>
-      <c r="G196" s="77" t="n"/>
-      <c r="H196" s="66" t="n"/>
+      <c r="B196" s="76" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C196" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/event-logs</t>
+        </is>
+      </c>
+      <c r="D196" s="77" t="inlineStr">
+        <is>
+          <t>Admin tra cứu nhật ký sự kiện kỹ thuật message bus (90 ngày)</t>
+        </is>
+      </c>
+      <c r="E196" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Query:
+{
+  "sourceService": "Commerce|Auction|User|Wallet",
+  "eventType": "OrderPaid",
+  "pageIndex": 1,
+  "pageSize": 20
+}</t>
+        </is>
+      </c>
+      <c r="F196" s="77" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "total": 1,
+  "items": [
+    {
+      "id": "uuid",
+      "eventId": "uuid",
+      "eventType": "OrderPaid",
+      "sourceService": "Commerce",
+      "actorId": "uuid",
+      "occurredAt": "2026-10-26T00:00:00Z"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G196" s="77" t="inlineStr">
+        <is>
+          <t>400 VAL_INVALID_FILTER: Query date range or filter is invalid.
+401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.</t>
+        </is>
+      </c>
+      <c r="H196" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-13</t>
+        </is>
+      </c>
       <c r="I196" s="77" t="n"/>
       <c r="J196" s="77" t="n"/>
       <c r="K196" s="77" t="n"/>
@@ -15701,13 +16318,63 @@
     </row>
     <row r="197" ht="15.75" customHeight="1" s="81">
       <c r="A197" s="9" t="n"/>
-      <c r="B197" s="9" t="n"/>
-      <c r="C197" s="21" t="n"/>
-      <c r="D197" s="21" t="n"/>
-      <c r="E197" s="21" t="n"/>
-      <c r="F197" s="21" t="n"/>
-      <c r="G197" s="21" t="n"/>
-      <c r="H197" s="66" t="n"/>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C197" s="21" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/event-logs/{id}</t>
+        </is>
+      </c>
+      <c r="D197" s="21" t="inlineStr">
+        <is>
+          <t>Admin xem chi tiết toàn bộ raw JSON payload của sự kiện kỹ thuật</t>
+        </is>
+      </c>
+      <c r="E197" s="21" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Path:
+{
+  "id": "uuid"
+}</t>
+        </is>
+      </c>
+      <c r="F197" s="21" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "id": "uuid",
+  "eventId": "uuid",
+  "eventType": "OrderPaid",
+  "sourceService": "Commerce",
+  "actorId": "uuid",
+  "payload": {
+    "orderId": "uuid",
+    "totalAmount": 480000
+  },
+  "occurredAt": "2026-10-26T00:00:00Z",
+  "createdAt": "2026-10-26T00:00:00Z"
+}</t>
+        </is>
+      </c>
+      <c r="G197" s="21" t="inlineStr">
+        <is>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.
+404 EVENT_LOG_NOT_FOUND: Event log entry was not found.</t>
+        </is>
+      </c>
+      <c r="H197" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-14</t>
+        </is>
+      </c>
       <c r="I197" s="21" t="n"/>
       <c r="J197" s="21" t="n"/>
       <c r="K197" s="21" t="n"/>
@@ -15730,13 +16397,65 @@
     </row>
     <row r="198" ht="15.75" customHeight="1" s="81">
       <c r="A198" s="76" t="n"/>
-      <c r="B198" s="76" t="n"/>
-      <c r="C198" s="77" t="n"/>
-      <c r="D198" s="77" t="n"/>
-      <c r="E198" s="77" t="n"/>
-      <c r="F198" s="77" t="n"/>
-      <c r="G198" s="77" t="n"/>
-      <c r="H198" s="66" t="n"/>
+      <c r="B198" s="76" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C198" s="77" t="inlineStr">
+        <is>
+          <t>/api/v1/admin/health/broker</t>
+        </is>
+      </c>
+      <c r="D198" s="77" t="inlineStr">
+        <is>
+          <t>Admin theo dõi trạng thái sức khỏe, latency và queue depth RabbitMQ</t>
+        </is>
+      </c>
+      <c r="E198" s="77" t="inlineStr">
+        <is>
+          <t>Header:
+{
+  "Authorization": "Bearer &lt;JWT&gt;"
+}
+Query:
+{
+  "limit": 50
+}</t>
+        </is>
+      </c>
+      <c r="F198" s="77" t="inlineStr">
+        <is>
+          <t>200 OK:
+{
+  "currentStatus": "UP",
+  "lastCheckedAt": "2026-10-26T00:00:00Z",
+  "latestLatencyMs": 5,
+  "latestQueueDepth": 0,
+  "history": [
+    {
+      "id": "uuid",
+      "brokerName": "rabbitmq",
+      "status": "UP",
+      "latencyMs": 5,
+      "queueDepth": 0,
+      "checkedAt": "2026-10-26T00:00:00Z"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G198" s="77" t="inlineStr">
+        <is>
+          <t>401 UNAUTHORIZED: Token is missing, expired, or invalid.
+403 FORBIDDEN: User does not have administrative permissions.</t>
+        </is>
+      </c>
+      <c r="H198" s="66" t="inlineStr">
+        <is>
+          <t>NOTI-16</t>
+        </is>
+      </c>
       <c r="I198" s="77" t="n"/>
       <c r="J198" s="77" t="n"/>
       <c r="K198" s="77" t="n"/>

--- a/docs/excel/flow_mock_excel.xlsx
+++ b/docs/excel/flow_mock_excel.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Response Standards" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="1075">
   <si>
     <t>user</t>
   </si>
@@ -65,12 +66,16 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Đăng ký thành công, vui lòng kiểm tra email để lấy mã OTP xác thực",
-"data": {
-"userId": "uuid",
-"email": "string",
-"otpExpiresIn": "int: 300"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Đăng ký thành công, vui lòng kiểm tra email để lấy mã OTP xác thực",
+  "data": {
+    "userId": "uuid",
+    "email": "string",
+    "otpExpiresIn": "int: 300"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -107,11 +112,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Kích hoạt tài khoản thành công! Bạn có thể đăng nhập ngay bây giờ",
-"data": {
-"isVerified": "boolean: true",
-"email": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Kích hoạt tài khoản thành công! Bạn có thể đăng nhập ngay bây giờ",
+  "data": {
+    "isVerified": "boolean: true",
+    "email": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -143,11 +152,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Mã OTP mới đã được gửi tới email của bạn",
-"data": {
-"email": "string",
-"resendCooldown": "int: 60"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Mã OTP mới đã được gửi tới email của bạn",
+  "data": {
+    "email": "string",
+    "resendCooldown": "int: 60"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -178,22 +191,26 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Đăng nhập thành công",
-"data": {
-"accessToken": "string",
-"refreshToken": "string",
-"tokenType": "Bearer",
-"expiresIn": 3600,
-"user": {
-"id": "uuid",
-"email": "string",
-"username": "string | null",
-"firstName": "string",
-"lastName": "string",
-"roles": "string[]",
-"permissions": "string[]"
-}
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Đăng nhập thành công",
+  "data": {
+    "accessToken": "string",
+    "refreshToken": "string",
+    "tokenType": "Bearer",
+    "expiresIn": 3600,
+    "user": {
+      "id": "uuid",
+      "email": "string",
+      "username": "string | null",
+      "firstName": "string",
+      "lastName": "string",
+      "roles": "string[]",
+      "permissions": "string[]"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -221,17 +238,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Làm mới phiên làm việc thành công",
-"data": {
-"accessToken": "string",
-"refreshToken": "string",
-"expiresIn": 3600
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Làm mới phiên làm việc thành công",
+  "data": {
+    "accessToken": "string",
+    "refreshToken": "string",
+    "expiresIn": 3600
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">401 ERR_INVALID_TOKEN: Token is invalid, expired, or malformed.
-401 ERR_TOKEN_REUSED: Token reuse attack detected. Session has been revoked.
+401 ERR_TOKEN_REUSED: Token reuse attack detected, session has been revoked.
 401 ERR_SESSION_REVOKED: Login session has been revoked.</t>
   </si>
   <si>
@@ -252,14 +273,18 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Nếu email tồn tại, hướng dẫn đặt lại mật khẩu đã được gửi đến bạn",
-"data": {
-"email": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Nếu email tồn tại, hướng dẫn đặt lại mật khẩu đã được gửi đến bạn",
+  "data": {
+    "email": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>429 ERR_RATE_LIMIT_EXCEEDED: Rate limit exceeded. Please try again later.</t>
+    <t>429 ERR_RATE_LIMIT_EXCEEDED: Rate limit exceeded, please try again later.</t>
   </si>
   <si>
     <t>AUTH-06</t>
@@ -288,10 +313,14 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Mật khẩu đã được đặt lại thành công. Vui lòng đăng nhập lại!",
-"data": {
-"success": true
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Mật khẩu đã được đặt lại thành công. Vui lòng đăng nhập lại!",
+  "data": {
+    "success": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -328,10 +357,14 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đổi mật khẩu thành công. Vui lòng đăng nhập lại trên các thiết bị khác",
-"data": {
-"success": true
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đổi mật khẩu thành công. Vui lòng đăng nhập lại trên các thiết bị khác",
+  "data": {
+    "success": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -360,10 +393,14 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đăng xuất thành công",
-"data": {
-"success": true
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đăng xuất thành công",
+  "data": {
+    "success": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -387,14 +424,18 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã đăng xuất khỏi toàn bộ các thiết bị khác thành công",
-"data": {
-"countRevoked": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã đăng xuất khỏi toàn bộ các thiết bị khác thành công",
+  "data": {
+    "countRevoked": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.</t>
+    <t>401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.</t>
   </si>
   <si>
     <t>USER-05</t>
@@ -411,16 +452,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách phiên đăng nhập thành công",
-"data": [
-{
-"sessionId": "uuid",
-"deviceInfo": "string",
-"ipAddress": "string",
-"lastActiveAt": "timestamp",
-"isCurrent": "boolean"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách phiên đăng nhập thành công",
+  "data": {
+    "items": [
+      {
+        "sessionId": "uuid",
+        "deviceInfo": "string",
+        "ipAddress": "string",
+        "lastActiveAt": "timestamp",
+        "isCurrent": "boolean"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -448,10 +503,14 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã thu hồi phiên đăng nhập thành công",
-"data": {
-"revokedSessionId": "uuid"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã thu hồi phiên đăng nhập thành công",
+  "data": {
+    "revokedSessionId": "uuid"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -470,27 +529,31 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy thông tin cá nhân thành công",
-"data": {
-"id": "uuid",
-"email": "string",
-"username": "string | null",
-"firstName": "string",
-"lastName": "string",
-"phoneNumber": "string",
-"avatarUrl": "string",
-"address": "string",
-"reputationScore": "int",
-"trustLevel": "string",
-"roles": "string[]",
-"permissions": "string[]",
-"isSeller": "boolean",
-"createdAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy thông tin cá nhân thành công",
+  "data": {
+    "id": "uuid",
+    "email": "string",
+    "username": "string | null",
+    "firstName": "string",
+    "lastName": "string",
+    "phoneNumber": "string",
+    "avatarUrl": "string",
+    "address": "string",
+    "reputationScore": "int",
+    "trustLevel": "string",
+    "roles": "string[]",
+    "permissions": "string[]",
+    "isSeller": "boolean",
+    "createdAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. Token is missing or expired.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, token is missing or expired.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
   <si>
@@ -524,17 +587,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật hồ sơ thành công",
-"data": {
-"id": "uuid",
-"username": "string | null",
-"firstName": "string",
-"lastName": "string",
-"phoneNumber": "string",
-"avatarUrl": "string",
-"address": "string",
-"updatedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật hồ sơ thành công",
+  "data": {
+    "id": "uuid",
+    "username": "string | null",
+    "firstName": "string",
+    "lastName": "string",
+    "phoneNumber": "string",
+    "avatarUrl": "string",
+    "address": "string",
+    "updatedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -554,11 +621,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy avatar thành công",
-"data": {
-"userId": "uuid",
-"avatarUrl": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy avatar thành công",
+  "data": {
+    "userId": "uuid",
+    "avatarUrl": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -580,16 +651,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật ảnh đại diện thành công",
-"data": {
-"avatarUrl": "string",
-"updatedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật ảnh đại diện thành công",
+  "data": {
+    "avatarUrl": "string",
+    "updatedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Unsupported file format. Only JPG, PNG, and WEBP are accepted.
-413 ERR_FILE_TOO_LARGE: File size exceeds maximum allowed limit of 5MB.
+    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Unsupported file format, only JPG, PNG, and WEBP are accepted.
+413 ERR_FILE_TOO_LARGE: File size exceeds maximum allowed limit of 5mb.
 500 ERR_STORAGE_UPLOAD_FAILED: Internal server error occurred while storing uploaded file.</t>
   </si>
   <si>
@@ -604,21 +679,25 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy thông tin uy tín cá nhân thành công",
-"data": {
-"userId": "uuid",
-"reputationScore": "int",
-"trustLevel": "string",
-"canBid": "boolean",
-"canSell": "boolean",
-"positiveRatingCount": "int",
-"negativeRatingCount": "int",
-"nextLevelThreshold": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy thông tin uy tín cá nhân thành công",
+  "data": {
+    "userId": "uuid",
+    "reputationScore": "int",
+    "trustLevel": "string",
+    "canBid": "boolean",
+    "canSell": "boolean",
+    "positiveRatingCount": "int",
+    "negativeRatingCount": "int",
+    "nextLevelThreshold": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. Token is invalid or missing.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, token is invalid or missing.
 404 ERR_USER_NOT_FOUND: User account was not found.</t>
   </si>
   <si>
@@ -647,30 +726,37 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy lịch sử vi phạm thành công",
-"data": {
-"items": [
-{
-"id": "uuid",
-"violationType": "string",
-"reason": "string",
-"penaltyApplied": "string",
-"pointsDeducted": "int",
-"status": "string",
-"issuedAt": "timestamp",
-"expiresAt": "timestamp"
-}
-],
-"pagination": {
-"total": "int",
-"page": "int",
-"limit": "int"
-}
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy lịch sử vi phạm thành công",
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "violationType": "string",
+        "reason": "string",
+        "penaltyApplied": "string",
+        "pointsDeducted": "int",
+        "status": "string",
+        "issuedAt": "timestamp",
+        "expiresAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>401 ERR_UNAUTHORIZED: Authentication required. Session is missing or expired.</t>
+    <t>401 ERR_UNAUTHORIZED: Authentication required, session is missing or expired.</t>
   </si>
   <si>
     <t>USER-09</t>
@@ -699,19 +785,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy thông tin hồ sơ công khai thành công",
-"data": {
-"id": "uuid",
-"username": "string | null",
-"firstName": "string",
-"lastName": "string",
-"avatarUrl": "string",
-"reputationScore": "int",
-"trustLevel": "string",
-"badges": "string[]",
-"isSeller": "boolean",
-"joinedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy thông tin hồ sơ công khai thành công",
+  "data": {
+    "id": "uuid",
+    "username": "string | null",
+    "firstName": "string",
+    "lastName": "string",
+    "avatarUrl": "string",
+    "reputationScore": "int",
+    "trustLevel": "string",
+    "badges": "string[]",
+    "isSeller": "boolean",
+    "joinedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -752,15 +842,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy thông tin cửa hàng thành công",
-"data": {
-"sellerId": "uuid",
-"shopName": "string",
-"avatarUrl": "string",
-"ratingAvg": "decimal",
-"totalReviews": "int",
-"joinedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy thông tin cửa hàng thành công",
+  "data": {
+    "sellerId": "uuid",
+    "shopName": "string",
+    "avatarUrl": "string",
+    "ratingAvg": "decimal",
+    "totalReviews": "int",
+    "joinedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -790,17 +884,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy tóm tắt uy tín thành công",
-"data": {
-"userId": "uuid",
-"reputationScore": "int",
-"trustLevel": "string",
-"badges": "string[]",
-"canBid": "boolean",
-"canSell": "boolean",
-"totalReviews": "int",
-"positiveRatio": "decimal"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy tóm tắt uy tín thành công",
+  "data": {
+    "userId": "uuid",
+    "reputationScore": "int",
+    "trustLevel": "string",
+    "badges": "string[]",
+    "canBid": "boolean",
+    "canSell": "boolean",
+    "totalReviews": "int",
+    "positiveRatio": "decimal"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -828,23 +926,35 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy lịch sử uy tín thành công",
-"data": {
-"items": [
-{
-"id": "int",
-"changeAmount": "int",
-"scoreAfter": "int",
-"reason": "string",
-"referenceType": "string",
-"createdAt": "timestamp"
-}
-]
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy lịch sử uy tín thành công",
+  "data": {
+    "items": [
+      {
+        "id": "int",
+        "changeAmount": "int",
+        "scoreAfter": "int",
+        "reason": "string",
+        "referenceType": "string",
+        "createdAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_FORBIDDEN: You do not have permission to view other users reputation history.</t>
   </si>
   <si>
@@ -884,21 +994,31 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách đánh giá thành công",
-"data": {
-"items": [
-{
-"id": "uuid",
-"reviewerName": "string",
-"rating": "int",
-"comment": "string",
-"mediaUrls": "string[]",
-"createdAt": "timestamp"
-}
-],
-"averageRating": "decimal",
-"totalReviews": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách đánh giá thành công",
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "reviewerName": "string",
+        "rating": "int",
+        "comment": "string",
+        "mediaUrls": "string[]",
+        "createdAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -923,15 +1043,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Upload ảnh đánh giá thành công",
-"data": {
-"fileUrls": "string[]"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Upload ảnh đánh giá thành công",
+  "data": {
+    "fileUrls": "string[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_FILE_LIMIT_EXCEEDED: Maximum limit of 5 attached images exceeded.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.</t>
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.</t>
   </si>
   <si>
     <t>FILE-02</t>
@@ -963,17 +1087,21 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Gửi đánh giá thành công! Điểm uy tín của đối tác đã được cập nhật",
-"data": {
-"reviewId": "uuid",
-"newTargetReputationScore": "int"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Gửi đánh giá thành công! Điểm uy tín của đối tác đã được cập nhật",
+  "data": {
+    "reviewId": "uuid",
+    "newTargetReputationScore": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_TRANSACTION_NOT_COMPLETED: Transaction is not yet completed.
 400 ERR_REVIEW_WINDOW_EXPIRED: Review submission period of 7 days has expired.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_NOT_TRANSACTION_PARTY: You are not a participant in this transaction.
 409 ERR_REVIEW_ALREADY_EXISTS: A review has already been submitted for this transaction.</t>
   </si>
@@ -1014,15 +1142,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Upload bằng chứng tố cáo thành công",
-"data": {
-"fileUrls": "string[]"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Upload bằng chứng tố cáo thành công",
+  "data": {
+    "fileUrls": "string[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Invalid file format. Only images up to 5MB are accepted.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.</t>
+    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Invalid file format, only images up to 5mb are accepted.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.</t>
   </si>
   <si>
     <t>FILE-01</t>
@@ -1052,18 +1184,22 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Gửi đơn tố cáo thành công. Nhân viên sẽ thụ lý trong 24h",
-"data": {
-"reportId": "uuid",
-"status": "PENDING",
-"submittedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Gửi đơn tố cáo thành công. Nhân viên sẽ thụ lý trong 24h",
+  "data": {
+    "reportId": "uuid",
+    "status": "PENDING",
+    "submittedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_CANNOT_REPORT_SELF: You cannot submit a report against yourself.
 400 ERR_VALIDATION_FAILED: Description content must be at least 10 characters long.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 404 ERR_USER_NOT_FOUND: Reported user does not exist.</t>
   </si>
   <si>
@@ -1090,31 +1226,38 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách tố cáo đã gửi thành công",
-"data": {
-"items": [
-{
-"reportId": "uuid",
-"targetType": "string",
-"targetId": "uuid",
-"reason": "string",
-"evidenceUrls": "string[]",
-"status": "string",
-"adminNote": "string",
-"createdAt": "timestamp",
-"resolvedAt": "timestamp"
-}
-],
-"pagination": {
-"total": "int",
-"page": "int",
-"limit": "int"
-}
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách tố cáo đã gửi thành công",
+  "data": {
+    "items": [
+      {
+        "reportId": "uuid",
+        "targetType": "string",
+        "targetId": "uuid",
+        "reason": "string",
+        "evidenceUrls": "string[]",
+        "status": "string",
+        "adminNote": "string",
+        "createdAt": "timestamp",
+        "resolvedAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>401 ERR_UNAUTHORIZED: Authentication required. Token is missing or expired.</t>
+    <t>401 ERR_UNAUTHORIZED: Authentication required, token is missing or expired.</t>
   </si>
   <si>
     <t>REPORT-05</t>
@@ -1147,21 +1290,25 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Hồ sơ mở Shop đã được tiếp nhận và chuyển sang trạng thái chờ duyệt",
-"data": {
-"registrationId": "uuid",
-"status": "PENDING_APPROVAL",
-"submittedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Hồ sơ mở Shop đã được tiếp nhận và chuyển sang trạng thái chờ duyệt",
+  "data": {
+    "registrationId": "uuid",
+    "status": "PENDING_APPROVAL",
+    "submittedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 ERR_GHN_WAREHOUSE_INVALID: GHN warehouse address is invalid.
+    <t xml:space="preserve">400 ERR_GHN_WAREHOUSE_INVALID: Ghn warehouse address is invalid.
 400 ERR_REPUTATION_TOO_LOW: Reputation score is insufficient to open a shop (minimum 50 required).
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 409 ERR_SHOP_NAME_TAKEN: Shop name already exists.
 409 ERR_REQUEST_ALREADY_PENDING: A registration request is already pending review.
-409 ERR_ALREADY_SELLER: User is already registered as a Seller.</t>
+409 ERR_ALREADY_SELLER: User is already registered as a seller.</t>
   </si>
   <si>
     <t>SELLER-01</t>
@@ -1195,15 +1342,19 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Mã OTP xác thực mở Shop đã được gửi lại tới email",
-"data": {
-"registrationId": "uuid",
-"cooldown": 60
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Mã OTP xác thực mở Shop đã được gửi lại tới email",
+  "data": {
+    "registrationId": "uuid",
+    "cooldown": 60
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 404 ERR_REGISTRATION_NOT_FOUND: Registration request was not found.
 429 ERR_OTP_COOLDOWN: Please wait at least 60 seconds before requesting another OTP.</t>
   </si>
@@ -1235,15 +1386,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Tải lên tài liệu định danh thành công",
-"data": {
-"documentUrls": "string[]"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Tải lên tài liệu định danh thành công",
+  "data": {
+    "documentUrls": "string[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Invalid document format. Only JPG, PNG, and PDF are accepted.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">400 ERR_INVALID_FILE_TYPE: Invalid document format, only JPG, PNG, and PDF are accepted.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 404 ERR_REGISTRATION_NOT_FOUND: Registration request was not found.</t>
   </si>
   <si>
@@ -1269,17 +1424,21 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Xác thực OTP thành công. Hồ sơ đã chuyển sang chờ Staff duyệt",
-"data": {
-"registrationId": "uuid",
-"status": "PENDING_APPROVAL"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Xác thực OTP thành công. Hồ sơ đã chuyển sang chờ Staff duyệt",
+  "data": {
+    "registrationId": "uuid",
+    "status": "PENDING_APPROVAL"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_OTP_INVALID: The OTP code provided is invalid.
 400 ERR_OTP_EXPIRED: The OTP code has expired.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 404 ERR_REGISTRATION_NOT_FOUND: Registration request was not found.</t>
   </si>
   <si>
@@ -1291,13 +1450,17 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy trạng thái hồ sơ thành công",
-"data": {
-"registrationId": "uuid",
-"status": "PENDING_APPROVAL | APPROVED | REJECTED",
-"rejectionReason": "string | null",
-"submittedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy trạng thái hồ sơ thành công",
+  "data": {
+    "registrationId": "uuid",
+    "status": "PENDING_APPROVAL | APPROVED | REJECTED",
+    "rejectionReason": "string | null",
+    "submittedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -1312,21 +1475,25 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy thông tin Shop thành công",
-"data": {
-"shopId": "uuid",
-"shopName": "string",
-"hotline": "string",
-"pickupAddress": "string",
-"ghnShopId": "string",
-"ratingAvg": "decimal",
-"totalProducts": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy thông tin Shop thành công",
+  "data": {
+    "shopId": "uuid",
+    "shopName": "string",
+    "hotline": "string",
+    "pickupAddress": "string",
+    "ghnShopId": "string",
+    "ratingAvg": "decimal",
+    "totalProducts": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
-403 ERR_FORBIDDEN_NOT_SELLER: Account does not have the Seller role.</t>
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
+403 ERR_FORBIDDEN_NOT_SELLER: Account does not have the seller role.</t>
   </si>
   <si>
     <t>SELLER-06</t>
@@ -1355,16 +1522,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật thông tin Shop thành công",
-"data": {
-"shopId": "uuid",
-"shopName": "string",
-"updatedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật thông tin Shop thành công",
+  "data": {
+    "shopId": "uuid",
+    "shopName": "string",
+    "updatedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_FORBIDDEN: You do not have permission to modify this shop.
 409 ERR_SHOP_NAME_TAKEN: Shop name is already taken.</t>
   </si>
@@ -1404,24 +1575,35 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách hồ sơ mở Shop thành công",
-"data": {
-"items": [
-{
-"registrationId": "uuid",
-"userId": "uuid",
-"shopName": "string",
-"identityCardNumber": "string",
-"warehouseAddress": "string",
-"reputationScore": "int"
-}
-],
-"total": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách hồ sơ mở Shop thành công",
+  "data": {
+    "items": [
+      {
+        "registrationId": "uuid",
+        "userId": "uuid",
+        "shopName": "string",
+        "identityCardNumber": "string",
+        "warehouseAddress": "string",
+        "reputationScore": "int"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view shop registration list.</t>
   </si>
   <si>
@@ -1449,25 +1631,29 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy chi tiết hồ sơ mở Shop thành công",
-"data": {
-"registrationId": "uuid",
-"userId": "uuid",
-"shopName": "string",
-"hotline": "string",
-"pickupAddress": "string",
-"identityCardNumber": "string",
-"idCardFrontUrl": "string",
-"idCardBackUrl": "string",
-"businessLicenseUrl": "string",
-"reputationScore": "int",
-"status": "string",
-"submittedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy chi tiết hồ sơ mở Shop thành công",
+  "data": {
+    "registrationId": "uuid",
+    "userId": "uuid",
+    "shopName": "string",
+    "hotline": "string",
+    "pickupAddress": "string",
+    "identityCardNumber": "string",
+    "idCardFrontUrl": "string",
+    "idCardBackUrl": "string",
+    "businessLicenseUrl": "string",
+    "reputationScore": "int",
+    "status": "string",
+    "submittedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view registration requests.
 404 ERR_REGISTRATION_NOT_FOUND: Registration request was not found.</t>
   </si>
@@ -1495,19 +1681,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Hồ sơ mở Shop đã được phê duyệt. Người dùng đã trở thành Seller",
-"data": {
-"registrationId": "uuid",
-"userId": "uuid",
-"status": "APPROVED",
-"approvedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Hồ sơ mở Shop đã được phê duyệt. Người dùng đã trở thành Seller",
+  "data": {
+    "registrationId": "uuid",
+    "userId": "uuid",
+    "status": "APPROVED",
+    "approvedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_REQUEST_NOT_PENDING: Registration request is not in a pending state.
 400 ERR_REPUTATION_TOO_LOW: Applicant reputation score has fallen below the threshold of 50.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to approve shop registrations.
 404 ERR_REQUEST_NOT_FOUND: Registration request was not found.</t>
   </si>
@@ -1547,18 +1737,22 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã từ chối hồ sơ mở Shop",
-"data": {
-"registrationId": "uuid",
-"status": "REJECTED",
-"rejectedAt": "timestamp",
-"rejectionReason": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã từ chối hồ sơ mở Shop",
+  "data": {
+    "registrationId": "uuid",
+    "status": "REJECTED",
+    "rejectedAt": "timestamp",
+    "rejectionReason": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_REASON_REQUIRED: Rejection reason must be at least 10 characters long.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to reject registration requests.
 404 ERR_REQUEST_NOT_FOUND: Registration request was not found.</t>
   </si>
@@ -1590,26 +1784,37 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách đơn tố cáo thành công",
-"data": {
-"items": [
-{
-"id": "uuid",
-"reporterId": "uuid",
-"reportedUserId": "uuid",
-"violationType": "string",
-"description": "string",
-"evidenceUrls": "string[]",
-"status": "string",
-"createdAt": "timestamp"
-}
-],
-"total": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách đơn tố cáo thành công",
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "reporterId": "uuid",
+        "reportedUserId": "uuid",
+        "violationType": "string",
+        "description": "string",
+        "evidenceUrls": "string[]",
+        "status": "string",
+        "createdAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to moderate reports.</t>
   </si>
   <si>
@@ -1638,17 +1843,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã xử lý tố cáo thành công. Chế tài kỷ luật đã được áp dụng",
-"data": {
-"reportId": "uuid",
-"status": "RESOLVED",
-"resolvedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã xử lý tố cáo thành công. Chế tài kỷ luật đã được áp dụng",
+  "data": {
+    "reportId": "uuid",
+    "status": "RESOLVED",
+    "resolvedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_ALREADY_RESOLVED: Report has already been resolved or processed.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to process reports.
 404 ERR_REPORT_NOT_FOUND: Report was not found.</t>
   </si>
@@ -1688,17 +1897,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã bác bỏ đơn tố cáo",
-"data": {
-"reportId": "uuid",
-"status": "DISMISSED",
-"dismissedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã bác bỏ đơn tố cáo",
+  "data": {
+    "reportId": "uuid",
+    "status": "DISMISSED",
+    "dismissedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_REASON_REQUIRED: A reason is required to dismiss the report.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to dismiss reports.
 404 ERR_REPORT_NOT_FOUND: Report was not found.</t>
   </si>
@@ -1729,16 +1942,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã ẩn đánh giá vi phạm thành công",
-"data": {
-"reviewId": "uuid",
-"isHidden": true
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã ẩn đánh giá vi phạm thành công",
+  "data": {
+    "reviewId": "uuid",
+    "isHidden": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_REASON_REQUIRED: A reason is required to hide the review.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to moderate reviews.
 404 ERR_REVIEW_NOT_FOUND: Review was not found.</t>
   </si>
@@ -1774,26 +1991,37 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh sách người dùng thành công",
-"data": {
-"items": [
-{
-"id": "uuid",
-"email": "string",
-"firstName": "string",
-"lastName": "string",
-"phoneNumber": "string",
-"status": "string",
-"reputationScore": "int",
-"roles": "string[]"
-}
-],
-"total": "int: 150"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh sách người dùng thành công",
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "email": "string",
+        "firstName": "string",
+        "lastName": "string",
+        "phoneNumber": "string",
+        "status": "string",
+        "reputationScore": "int",
+        "roles": "string[]"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view user list.</t>
   </si>
   <si>
@@ -1822,17 +2050,21 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"msg": "Tạo tài khoản thành công",
-"data": {
-"userId": "uuid",
-"email": "string",
-"roles": "string[]"
-}
+  "success": true,
+  "statusCode": 201,
+  "message": "Tạo tài khoản thành công",
+  "data": {
+    "userId": "uuid",
+    "email": "string",
+    "roles": "string[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_INVALID_ROLES: The specified role list is invalid.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to create user accounts.
 409 ERR_EMAIL_EXISTS: Email already exists in the system.</t>
   </si>
@@ -1864,26 +2096,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy chi tiết người dùng thành công",
-"data": {
-"id": "uuid",
-"email": "string",
-"firstName": "string",
-"lastName": "string",
-"phoneNumber": "string",
-"status": "string",
-"reputationScore": "int",
-"trustLevel": "string",
-"roles": "string[]",
-"permissions": "string[]",
-"sellerProfile": "object",
-"createdAt": "timestamp",
-"auditHistory": "object[]"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy chi tiết người dùng thành công",
+  "data": {
+    "id": "uuid",
+    "email": "string",
+    "firstName": "string",
+    "lastName": "string",
+    "phoneNumber": "string",
+    "status": "string",
+    "reputationScore": "int",
+    "trustLevel": "string",
+    "roles": "string[]",
+    "permissions": "string[]",
+    "sellerProfile": "object",
+    "createdAt": "timestamp",
+    "auditHistory": "object[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view user details.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
@@ -1912,20 +2148,24 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật thông tin người dùng thành công",
-"data": {
-"id": "uuid",
-"firstName": "string",
-"lastName": "string",
-"status": "string",
-"updatedBy": "uuid",
-"updatedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật thông tin người dùng thành công",
+  "data": {
+    "id": "uuid",
+    "firstName": "string",
+    "lastName": "string",
+    "status": "string",
+    "updatedBy": "uuid",
+    "updatedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_AUDIT_REASON_REQUIRED: Intervention reason must be at least 10 characters long.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to edit user information.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
@@ -1950,17 +2190,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Tài khoản người dùng đã được xóa mềm thành công",
-"data": {
-"id": "uuid",
-"isDeleted": true,
-"deletedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Tài khoản người dùng đã được xóa mềm thành công",
+  "data": {
+    "id": "uuid",
+    "isDeleted": true,
+    "deletedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_CANNOT_DELETE_ADMIN: Cannot delete an administrator account.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to delete user accounts.
 404 ERR_USER_NOT_FOUND: User was not found.
 409 ERR_ACTIVE_AUCTIONS_EXIST: Account currently has active auctions or pending orders.</t>
@@ -1999,19 +2243,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã khóa tài khoản người dùng thành công",
-"data": {
-"id": "uuid",
-"status": "BANNED",
-"bannedUntil": "timestamp",
-"reason": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã khóa tài khoản người dùng thành công",
+  "data": {
+    "id": "uuid",
+    "status": "BANNED",
+    "bannedUntil": "timestamp",
+    "reason": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_CANNOT_BAN_ADMIN: Cannot ban or lock an administrator account.
 400 ERR_ALREADY_BANNED: Account is already banned or locked.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to ban users.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
@@ -2048,17 +2296,21 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Đã mở khóa tài khoản người dùng thành công",
-"data": {
-"id": "uuid",
-"status": "ACTIVE",
-"unbannedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Đã mở khóa tài khoản người dùng thành công",
+  "data": {
+    "id": "uuid",
+    "status": "ACTIVE",
+    "unbannedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_USER_NOT_BANNED: Account is currently active and not banned.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to unban users.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
@@ -2077,20 +2329,24 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy chi tiết Shop thành công",
-"data": {
-"sellerId": "uuid",
-"shopName": "string",
-"ownerUserId": "uuid",
-"identityCardNumber": "string",
-"pickupAddress": "string",
-"status": "string",
-"auditHistory": "object[]"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy chi tiết Shop thành công",
+  "data": {
+    "sellerId": "uuid",
+    "shopName": "string",
+    "ownerUserId": "uuid",
+    "identityCardNumber": "string",
+    "pickupAddress": "string",
+    "status": "string",
+    "auditHistory": "object[]"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_FORBIDDEN: Administrator privileges are required.
 404 ERR_SELLER_NOT_FOUND: Shop information was not found.</t>
   </si>
@@ -2120,21 +2376,25 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật vai trò người dùng thành công",
-"data": {
-"userId": "uuid",
-"roles": [
-"STAFF"
-],
-"updatedBy": "uuid"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật vai trò người dùng thành công",
+  "data": {
+    "userId": "uuid",
+    "roles": [
+      "STAFF"
+    ],
+    "updatedBy": "uuid"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_SOD_VIOLATION: Separation of duties (SoD) policy violation detected.
 400 ERR_CANNOT_DEMOTE_LAST_ADMIN: Cannot demote the last remaining administrator.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
-403 ERR_FORBIDDEN: Only Super Admin has permission to assign roles.</t>
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
+403 ERR_FORBIDDEN: Only super admin has permission to assign roles.</t>
   </si>
   <si>
     <t>ADMIN-10</t>
@@ -2161,20 +2421,24 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Điều chỉnh điểm uy tín người dùng thành công",
-"data": {
-"userId": "uuid",
-"previousScore": "int",
-"newScore": "int",
-"delta": "int",
-"trustLevel": "string"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Điều chỉnh điểm uy tín người dùng thành công",
+  "data": {
+    "userId": "uuid",
+    "previousScore": "int",
+    "newScore": "int",
+    "delta": "int",
+    "trustLevel": "string"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_REASON_REQUIRED: Reputation adjustment reason must be at least 10 characters long.
 400 ERR_INVALID_DELTA: Reputation delta must be non-zero and within [-50, +50].
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to adjust reputation scores.
 404 ERR_USER_NOT_FOUND: User was not found.</t>
   </si>
@@ -2199,20 +2463,34 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh mục vai trò thành công",
-"data": [
-{
-"roleId": "int",
-"roleName": "string",
-"description": "string",
-"isSystemRole": "boolean",
-"permissionsCount": "int"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh mục vai trò thành công",
+  "data": {
+    "items": [
+      {
+        "roleId": "int",
+        "roleName": "string",
+        "description": "string",
+        "isSystemRole": "boolean",
+        "permissionsCount": "int"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view roles.</t>
   </si>
   <si>
@@ -2227,19 +2505,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy danh mục đặc quyền thành công",
-"data": [
-{
-"permissionId": "int",
-"permissionCode": "string",
-"module": "string",
-"description": "string"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy danh mục đặc quyền thành công",
+  "data": {
+    "items": [
+      {
+        "permissionId": "int",
+        "permissionCode": "string",
+        "module": "string",
+        "description": "string"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view permissions.</t>
   </si>
   <si>
@@ -2267,16 +2559,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật quyền hạn vai trò thành công",
-"data": {
-"roleId": "int",
-"updatedPermissionsCount": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật quyền hạn vai trò thành công",
+  "data": {
+    "roleId": "int",
+    "updatedPermissionsCount": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_CANNOT_EDIT_SYSTEM_ROLE: System-defined roles cannot be edited or modified.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to edit roles.
 404 ERR_ROLE_NOT_FOUND: Specified role does not exist.</t>
   </si>
@@ -2307,22 +2603,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "id": "uuid",
-      "actorId": "uuid",
-      "action": "USER_BANNED",
-      "targetEntity": "users",
-      "oldValues": {},
-      "newValues": {},
-      "reason": "Policy violation.",
-      "ipAddress": "127.0.0.1",
-      "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "actorId": "uuid",
+        "action": "USER_BANNED",
+        "targetEntity": "users",
+        "oldValues": {},
+        "newValues": {},
+        "reason": "Policy violation.",
+        "ipAddress": "127.0.0.1",
+        "createdAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
     }
-  ],
-  "total": 1,
-  "page": 1,
-  "limit": 20
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2341,20 +2648,34 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Lấy cấu hình hệ thống thành công",
-"data": [
-{
-"key": "string",
-"value": "string",
-"description": "string",
-"dataType": "string",
-"updatedAt": "timestamp"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "message": "Lấy cấu hình hệ thống thành công",
+  "data": {
+    "items": [
+      {
+        "key": "string",
+        "value": "string",
+        "description": "string",
+        "dataType": "string",
+        "updatedAt": "timestamp"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+    <t xml:space="preserve">401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to view system configurations.</t>
   </si>
   <si>
@@ -2381,18 +2702,22 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"msg": "Cập nhật cấu hình sàn thành công",
-"data": {
-"key": "string",
-"oldValue": "string",
-"newValue": "string",
-"updatedAt": "timestamp"
-}
+  "success": true,
+  "statusCode": 200,
+  "message": "Cập nhật cấu hình sàn thành công",
+  "data": {
+    "key": "string",
+    "oldValue": "string",
+    "newValue": "string",
+    "updatedAt": "timestamp"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 ERR_INVALID_CONFIG_VALUE: Configuration parameter value is invalid.
-401 ERR_UNAUTHORIZED: Authentication required. User is not logged in.
+401 ERR_UNAUTHORIZED: Authentication required, user is not logged in.
 403 ERR_PERMISSION_DENIED: You do not have permission to edit system configurations.
 404 ERR_CONFIG_NOT_FOUND: Configuration key was not found.</t>
   </si>
@@ -2406,7 +2731,10 @@
     <t>AUC-17 (áp dụng cấu hình đấu giá mới)</t>
   </si>
   <si>
-    <t>F1. mua hàng thường</t>
+    <t>F1. mua hàng thường.</t>
+  </si>
+  <si>
+    <t>Error.</t>
   </si>
   <si>
     <t>/api/v1/products</t>
@@ -2430,21 +2758,32 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"productId": "uuid",
-"name": "string",
-"brand": "string",
-"minPrice": "decimal",
-"maxPrice": "decimal",
-"primaryImageUrl": "string",
-"avgRating": "decimal",
-"status": "DRAFT|ACTIVE|INACTIVE"
-}
-],
-"page": "int",
-"pageSize": "int",
-"total": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "productId": "uuid",
+        "name": "string",
+        "brand": "string",
+        "minPrice": "decimal",
+        "maxPrice": "decimal",
+        "primaryImageUrl": "string",
+        "avgRating": "decimal",
+        "status": "DRAFT|ACTIVE|INACTIVE"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2478,19 +2817,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"productId": "uuid",
-"name": "string",
-"minPrice": "decimal",
-"maxPrice": "decimal",
-"primaryImageUrl": "string",
-"avgRating": "decimal"
-}
-],
-"page": "int",
-"pageSize": "int",
-"total": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "productId": "uuid",
+        "name": "string",
+        "minPrice": "decimal",
+        "maxPrice": "decimal",
+        "primaryImageUrl": "string",
+        "avgRating": "decimal"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2518,40 +2868,59 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"product": {
-"productId": "uuid",
-"sellerId": "uuid",
-"categoryId": "uuid",
-"name": "string",
-"description": "string",
-"brand": "string",
-"saleType": "REGULAR|AUCTION",
-"status": "DRAFT|ACTIVE|INACTIVE",
-"statusReason": "SELLER_PAUSED|DISCONTINUED|ADMIN_LOCKED|OTHER",
-"specifications": "object",
-"publishedAt": "datetime"
-},
-"category": {
-"categoryId": "uuid",
-"parentId": "uuid",
-"name": "string",
-"description": "string",
-"level": "int",
-"sortOrder": "int",
-"isActive": "boolean"
-},
-"variants": [
-{
-"variantId": "uuid",
-"skuCode": "string",
-"name": "string",
-"price": "decimal",
-"status": "ACTIVE|INACTIVE",
-"attributes": [{"attrName": "string", "attrValue": "string"}]
-}
-],
-"images": [{"url": "string", "altText": "string"}],
-"rating": {"avgRating": "decimal", "reviewCount": "int"}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "product": {
+      "productId": "uuid",
+      "sellerId": "uuid",
+      "categoryId": "uuid",
+      "name": "string",
+      "description": "string",
+      "brand": "string",
+      "saleType": "REGULAR|AUCTION",
+      "status": "DRAFT|ACTIVE|INACTIVE",
+      "statusReason": "SELLER_PAUSED|DISCONTINUED|ADMIN_LOCKED|OTHER",
+      "specifications": "object",
+      "publishedAt": "datetime"
+    },
+    "category": {
+      "categoryId": "uuid",
+      "parentId": "uuid",
+      "name": "string",
+      "description": "string",
+      "level": "int",
+      "sortOrder": "int",
+      "isActive": "boolean"
+    },
+    "variants": [
+      {
+        "variantId": "uuid",
+        "skuCode": "string",
+        "name": "string",
+        "price": "decimal",
+        "status": "ACTIVE|INACTIVE",
+        "attributes": [
+          {
+            "attrName": "string",
+            "attrValue": "string"
+          }
+        ]
+      }
+    ],
+    "images": [
+      {
+        "url": "string",
+        "altText": "string"
+      }
+    ],
+    "rating": {
+      "avgRating": "decimal",
+      "reviewCount": "int"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2578,10 +2947,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"cartItemId": "uuid",
-"quantity": "int",
-"unitPriceSnapshot": "decimal",
-"cart": {"itemCount": "int", "subtotalAmount": "decimal"}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "cartItemId": "uuid",
+    "quantity": "int",
+    "unitPriceSnapshot": "decimal",
+    "cart": {
+      "itemCount": "int",
+      "subtotalAmount": "decimal"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2616,35 +2994,43 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"cartId": "uuid",
-"status": "Active|Abandoned|Converted",
-"itemCount": "int",
-"subtotalAmount": "decimal",
-"lastActivityAt": "datetime",
-"groups": [
-{
-"sellerId": "uuid",
-"sellerName": "string",
-"items": [
-{
-"cartItemId": "uuid",
-"productId": "uuid",
-"skuId": "uuid",
-"productName": "string",
-"skuAttributes": "object",
-"imageUrl": "string",
-"quantity": "int",
-"unitPriceSnapshot": "decimal",
-"currentUnitPrice": "decimal",
-"lineTotal": "decimal",
-"priceChanged": "boolean",
-"stockAvailable": "int",
-"itemStatus": "OK|OUT_OF_STOCK|INACTIVE|PRICE_CHANGED"
-}
-]
-}
-],
-"warnings": ["CATALOG_UNAVAILABLE|FULFILLMENT_UNAVAILABLE"]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "cartId": "uuid",
+    "status": "Active|Abandoned|Converted",
+    "itemCount": "int",
+    "subtotalAmount": "decimal",
+    "lastActivityAt": "datetime",
+    "groups": [
+      {
+        "sellerId": "uuid",
+        "sellerName": "string",
+        "items": [
+          {
+            "cartItemId": "uuid",
+            "productId": "uuid",
+            "skuId": "uuid",
+            "productName": "string",
+            "skuAttributes": "object",
+            "imageUrl": "string",
+            "quantity": "int",
+            "unitPriceSnapshot": "decimal",
+            "currentUnitPrice": "decimal",
+            "lineTotal": "decimal",
+            "priceChanged": "boolean",
+            "stockAvailable": "int",
+            "itemStatus": "OK|OUT_OF_STOCK|INACTIVE|PRICE_CHANGED"
+          }
+        ]
+      }
+    ],
+    "warnings": [
+      "CATALOG_UNAVAILABLE|FULFILLMENT_UNAVAILABLE"
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2682,10 +3068,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"cartItemId": "uuid",
-"quantity": "int",
-"lineTotal": "decimal",
-"cart": {"itemCount": "int", "subtotalAmount": "decimal"}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "cartItemId": "uuid",
+    "quantity": "int",
+    "lineTotal": "decimal",
+    "cart": {
+      "itemCount": "int",
+      "subtotalAmount": "decimal"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2703,7 +3098,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"cart": {"itemCount": "int", "subtotalAmount": "decimal"}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "cart": {
+      "itemCount": "int",
+      "subtotalAmount": "decimal"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2731,8 +3135,17 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"removedCount": "int",
-"cart": {"itemCount": "int", "subtotalAmount": "decimal"}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "removedCount": "int",
+    "cart": {
+      "itemCount": "int",
+      "subtotalAmount": "decimal"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2757,15 +3170,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"valid": "boolean",
-"items": [
-{
-"cartItemId": "uuid",
-"issues": ["PRICE_CHANGED|OUT_OF_STOCK|INACTIVE|SELLER_SUSPENDED|QTY_EXCEEDS_STOCK"],
-"currentUnitPrice": "decimal",
-"availableQty": "int"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "cartItemId": "uuid",
+        "issues": [
+          "PRICE_CHANGED|OUT_OF_STOCK|INACTIVE|SELLER_SUSPENDED|QTY_EXCEEDS_STOCK"
+        ],
+        "currentUnitPrice": "decimal",
+        "availableQty": "int"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2811,32 +3239,45 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"orders": [
-{
-"sellerId": "uuid",
-"items": "array",
-"itemsAmount": "decimal",
-"productDiscountAmount": "decimal",
-"shopDiscountAmount": "decimal",
-"platformMarkupAmount": "decimal",
-"systemDiscountAmount": "decimal",
-"shippingFeeAmount": "decimal",
-"totalAmount": "decimal",
-"shippingOptions": [
-{
-"fee": "decimal",
-"serviceType": "Standard|Express|SameDay",
-"estimatedDeliveryAt": "datetime"
-}
-],
-"quoteId": "string"
-}
-],
-"grandTotal": "decimal",
-"appliedVouchers": "array",
-"invalidVouchers": [{"code": "string", "reason": "string"}],
-"walletBalance": "decimal",
-"warnings": ["SHIPPING_QUOTE_UNAVAILABLE"]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "orders": [
+      {
+        "sellerId": "uuid",
+        "items": "array",
+        "itemsAmount": "decimal",
+        "productDiscountAmount": "decimal",
+        "shopDiscountAmount": "decimal",
+        "platformMarkupAmount": "decimal",
+        "systemDiscountAmount": "decimal",
+        "shippingFeeAmount": "decimal",
+        "totalAmount": "decimal",
+        "shippingOptions": [
+          {
+            "fee": "decimal",
+            "serviceType": "Standard|Express|SameDay",
+            "estimatedDeliveryAt": "datetime"
+          }
+        ],
+        "quoteId": "string"
+      }
+    ],
+    "grandTotal": "decimal",
+    "appliedVouchers": "array",
+    "invalidVouchers": [
+      {
+        "code": "string",
+        "reason": "string"
+      }
+    ],
+    "walletBalance": "decimal",
+    "warnings": [
+      "SHIPPING_QUOTE_UNAVAILABLE"
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2877,14 +3318,22 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "orderId": "uuid",
-  "orderNo": "ORD-20261026-0001",
-  "totalAmount": 480000,
-  "status": "PENDING_PAYMENT",
-  "paymentDeadlineAt": "2026-10-26T02:00:00Z",
-  "paymentUrl": null,
-  "subOrderIds": ["uuid"],
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "orderId": "uuid",
+    "orderNo": "ORD-20261026-0001",
+    "totalAmount": 480000,
+    "status": "PENDING_PAYMENT",
+    "paymentDeadlineAt": "2026-10-26T02:00:00Z",
+    "paymentUrl": null,
+    "subOrderIds": [
+      "uuid"
+    ],
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -2930,41 +3379,47 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "orderId": "uuid",
-  "orderNo": "ORD-20261026-0001",
-  "buyerId": "uuid",
-  "status": "PENDING_PAYMENT",
-  "totalAmount": 480000,
-  "paymentMethod": "WALLET",
-  "shippingAddress": "123 Le Loi, Ben Nghe, Quan 1, TP.HCM",
-  "contactPhone": "0901234567",
-  "subOrders": [
-    {
-      "subOrderId": "uuid",
-      "subOrderNo": "SUB-20261026-0001",
-      "sellerId": "uuid",
-      "shopName": "Shop Cong Nghe",
-      "status": "PENDING_PAYMENT",
-      "itemsAmount": 500000,
-      "shippingFee": 30000,
-      "discountAmount": 50000,
-      "totalAmount": 480000,
-      "items": [
-        {
-          "orderItemId": "uuid",
-          "productId": "uuid",
-          "skuId": "uuid",
-          "productName": "Chuot gaming khong day",
-          "skuCode": "MOUSE-WL-01",
-          "imageUrl": "https://img.example.com/mouse.png",
-          "quantity": 1,
-          "unitPrice": 500000,
-          "lineTotal": 500000
-        }
-      ]
-    }
-  ],
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "orderId": "uuid",
+    "orderNo": "ORD-20261026-0001",
+    "buyerId": "uuid",
+    "status": "PENDING_PAYMENT",
+    "totalAmount": 480000,
+    "paymentMethod": "WALLET",
+    "shippingAddress": "123 Le Loi, Ben Nghe, Quan 1, TP.HCM",
+    "contactPhone": "0901234567",
+    "subOrders": [
+      {
+        "subOrderId": "uuid",
+        "subOrderNo": "SUB-20261026-0001",
+        "sellerId": "uuid",
+        "shopName": "Shop Cong Nghe",
+        "status": "PENDING_PAYMENT",
+        "itemsAmount": 500000,
+        "shippingFee": 30000,
+        "discountAmount": 50000,
+        "totalAmount": 480000,
+        "items": [
+          {
+            "orderItemId": "uuid",
+            "productId": "uuid",
+            "skuId": "uuid",
+            "productName": "Chuot gaming khong day",
+            "skuCode": "MOUSE-WL-01",
+            "imageUrl": "https://img.example.com/mouse.png",
+            "quantity": 1,
+            "unitPrice": 500000,
+            "lineTotal": 500000
+          }
+        ]
+      }
+    ],
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3000,32 +3455,32 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "subOrderId": "uuid",
-  "subOrderNo": "SUB-20261026-0001",
-  "orderId": "uuid",
-  "sellerId": "uuid",
-  "buyerId": "uuid",
-  "status": "PAID",
-  "itemsAmount": 500000,
-  "shippingFeeAmount": 30000,
-  "shopDiscountAmount": 50000,
-  "sellerReceiveAmount": 465000,
-  "platformFeeAmount": 15000,
-  "totalAmount": 480000,
-  "items": [
-    {
-      "orderItemId": "uuid",
-      "productId": "uuid",
-      "skuId": "uuid",
-      "productName": "Chuot gaming khong day",
-      "skuCode": "MOUSE-WL-01",
-      "quantity": 1,
-      "unitPrice": 500000,
-      "lineTotal": 500000
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "orderItemId": "uuid",
+        "productId": "uuid",
+        "skuId": "uuid",
+        "productName": "Chuot gaming khong day",
+        "skuCode": "MOUSE-WL-01",
+        "quantity": 1,
+        "unitPrice": 500000,
+        "lineTotal": 500000
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ],
-  "sellerRespondDeadlineAt": "2026-10-27T00:00:00Z",
-  "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3060,10 +3515,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "orderId": "uuid",
-  "status": "CANCELLED",
-  "cancelledAt": "2026-10-26T00:00:00Z",
-  "message": "Order has been successfully cancelled."
+  "success": true,
+  "statusCode": 200,
+  "message": "Order has been successfully cancelled.",
+  "data": {
+    "orderId": "uuid",
+    "status": "CANCELLED",
+    "cancelledAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3106,7 +3567,13 @@
     <t xml:space="preserve">200 OK:
 {
   "success": true,
-  "message": "Payment webhook processed successfully."
+  "statusCode": 200,
+  "message": "Payment webhook processed successfully.",
+  "data": {
+    "success": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3192,9 +3659,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "subOrderId": "uuid",
-  "status": "SELLER_ACCEPTED",
-  "acceptedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "subOrderId": "uuid",
+    "status": "SELLER_ACCEPTED",
+    "acceptedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3246,9 +3719,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "subOrderId": "uuid",
-  "status": "REJECTED",
-  "rejectedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "subOrderId": "uuid",
+    "status": "REJECTED",
+    "rejectedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3309,33 +3788,39 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "shipmentId": "uuid",
-  "orderId": "uuid",
-  "subOrderId": "uuid",
-  "carrierName": "GHN",
-  "trackingNumber": "GHN1029384756",
-  "status": "IN_TRANSIT",
-  "shippingFee": 30000,
-  "codAmount": 0,
-  "receiverName": "Nguyen Van A",
-  "receiverPhone": "0901234567",
-  "receiverAddress": "123 Le Loi, Ben Nghe, Quan 1, TP.HCM",
-  "events": [
-    {
-      "status": "PICKED_UP",
-      "location": "Kho Tan Binh",
-      "description": "Shipper picked up parcel from seller.",
-      "eventAt": "2026-10-26T08:00:00Z"
-    },
-    {
-      "status": "IN_TRANSIT",
-      "location": "Kho HN SOC",
-      "description": "Parcel is in transit to distribution hub.",
-      "eventAt": "2026-10-26T12:00:00Z"
-    }
-  ],
-  "estimatedDeliveryAt": "2026-10-28T18:00:00Z",
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "shipmentId": "uuid",
+    "orderId": "uuid",
+    "subOrderId": "uuid",
+    "carrierName": "GHN",
+    "trackingNumber": "GHN1029384756",
+    "status": "IN_TRANSIT",
+    "shippingFee": 30000,
+    "codAmount": 0,
+    "receiverName": "Nguyen Van A",
+    "receiverPhone": "0901234567",
+    "receiverAddress": "123 Le Loi, Ben Nghe, Quan 1, TP.HCM",
+    "events": [
+      {
+        "status": "PICKED_UP",
+        "location": "Kho Tan Binh",
+        "description": "Shipper picked up parcel from seller.",
+        "eventAt": "2026-10-26T08:00:00Z"
+      },
+      {
+        "status": "IN_TRANSIT",
+        "location": "Kho HN SOC",
+        "description": "Parcel is in transit to distribution hub.",
+        "eventAt": "2026-10-26T12:00:00Z"
+      }
+    ],
+    "estimatedDeliveryAt": "2026-10-28T18:00:00Z",
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3354,18 +3839,24 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "orderId": "uuid",
-  "shipments": [
-    {
-      "shipmentId": "uuid",
-      "subOrderId": "uuid",
-      "carrierName": "GHN",
-      "trackingNumber": "GHN1029384756",
-      "status": "IN_TRANSIT",
-      "shippingFee": 30000,
-      "estimatedDeliveryAt": "2026-10-28T18:00:00Z"
-    }
-  ]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "orderId": "uuid",
+    "shipments": [
+      {
+        "shipmentId": "uuid",
+        "subOrderId": "uuid",
+        "carrierName": "GHN",
+        "trackingNumber": "GHN1029384756",
+        "status": "IN_TRANSIT",
+        "shippingFee": 30000,
+        "estimatedDeliveryAt": "2026-10-28T18:00:00Z"
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3402,23 +3893,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "shipmentId": "uuid",
-      "subOrderId": "uuid",
-      "trackingNumber": "GHN1029384756",
-      "carrierName": "GHN",
-      "status": "READY_TO_SHIP",
-      "shippingFee": 30000,
-      "receiverName": "Nguyen Van A",
-      "receiverPhone": "0901234567",
-      "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "shipmentId": "uuid",
+        "subOrderId": "uuid",
+        "trackingNumber": "GHN1029384756",
+        "carrierName": "GHN",
+        "status": "READY_TO_SHIP",
+        "shippingFee": 30000,
+        "receiverName": "Nguyen Van A",
+        "receiverPhone": "0901234567",
+        "createdAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ],
-  "page": 1,
-  "size": 20,
-  "totalItems": 1,
-  "totalPages": 1
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3452,21 +3953,31 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "shipmentId": "uuid",
-      "trackingNumber": "GHN1029384756",
-      "subOrderId": "uuid",
-      "carrierName": "GHN",
-      "status": "IN_TRANSIT",
-      "receiverName": "Nguyen Van A",
-      "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "shipmentId": "uuid",
+        "trackingNumber": "GHN1029384756",
+        "subOrderId": "uuid",
+        "carrierName": "GHN",
+        "status": "IN_TRANSIT",
+        "receiverName": "Nguyen Van A",
+        "createdAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ],
-  "page": 1,
-  "size": 20,
-  "totalItems": 1,
-  "totalPages": 1
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3483,22 +3994,27 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "shipmentId": "uuid",
-  "subOrderId": "uuid",
-  "carrierName": "GHN",
-  "trackingNumber": "GHN1029384756",
-  "status": "READY_TO_SHIP",
-  "receiverName": "Nguyen Van A",
-  "receiverPhone": "0901234567",
-  "receiverAddress": "123 Le Loi, Ben Nghe, Quan 1, TP.HCM",
-  "items": [
-    {
-      "skuId": "uuid",
-      "productName": "Chuot gaming khong day",
-      "quantity": 1
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "skuId": "uuid",
+        "productName": "Chuot gaming khong day",
+        "quantity": 1
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ],
-  "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3535,10 +4051,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "shipmentId": "uuid",
-  "trackingNumber": "GHN1029384756",
-  "currentStatus": "OUT_FOR_DELIVERY",
-  "updatedAt": "2026-10-26T14:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "shipmentId": "uuid",
+    "trackingNumber": "GHN1029384756",
+    "currentStatus": "OUT_FOR_DELIVERY",
+    "updatedAt": "2026-10-26T14:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3578,12 +4100,18 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "reviewId": "uuid",
-  "orderId": "uuid",
-  "productId": "uuid",
-  "rating": 5,
-  "comment": "San pham rat tot, dong goi ky.",
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "reviewId": "uuid",
+    "orderId": "uuid",
+    "productId": "uuid",
+    "rating": 5,
+    "comment": "San pham rat tot, dong goi ky.",
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3633,11 +4161,17 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "feedbackId": "uuid",
-  "orderId": "uuid",
-  "targetUserId": "uuid",
-  "rating": 5,
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "feedbackId": "uuid",
+    "orderId": "uuid",
+    "targetUserId": "uuid",
+    "rating": 5,
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3683,12 +4217,18 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "reviewId": "uuid",
-  "orderId": "uuid",
-  "productId": "uuid",
-  "rating": 4,
-  "comment": "Cap nhat: San pham dung tot sau 1 tuan.",
-  "updatedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "reviewId": "uuid",
+    "orderId": "uuid",
+    "productId": "uuid",
+    "rating": 4,
+    "comment": "Cap nhat: San pham dung tot sau 1 tuan.",
+    "updatedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3723,11 +4263,17 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "feedbackId": "uuid",
-  "orderId": "uuid",
-  "targetUserId": "uuid",
-  "rating": 4,
-  "updatedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "feedbackId": "uuid",
+    "orderId": "uuid",
+    "targetUserId": "uuid",
+    "rating": 4,
+    "updatedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3745,9 +4291,15 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "shipmentId": "uuid",
-  "status": "COMPLETED",
-  "completedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "shipmentId": "uuid",
+    "status": "COMPLETED",
+    "completedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3795,7 +4347,13 @@
     <t xml:space="preserve">200 OK:
 {
   "success": true,
-  "message": "Webhook event processed."
+  "statusCode": 200,
+  "message": "Webhook event processed.",
+  "data": {
+    "success": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3844,10 +4402,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "subOrderId": "uuid",
-  "refundAmount": 480000,
-  "status": "REFUNDED",
-  "refundedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "subOrderId": "uuid",
+    "refundAmount": 480000,
+    "status": "REFUNDED",
+    "refundedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -3880,10 +4444,10 @@
     <t>ORD-14: ORD-18 CAS order sang REFUNDED, ghi history, outbox OrderRefundCompleted; RefundFailed thì báo Support đối soát (thịnh)</t>
   </si>
   <si>
-    <t>F2. quản lý sản phẩm</t>
-  </si>
-  <si>
-    <t>Erorr</t>
+    <t>F2. quản lý sản phẩm.</t>
+  </si>
+  <si>
+    <t>Erorr.</t>
   </si>
   <si>
     <t>xem toàn bộ các sản phẩm của shop mình</t>
@@ -3909,29 +4473,40 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"productId": "uuid",
-"name": "string",
-"brand": "string",
-"saleType": "REGULAR|AUCTION",
-"minPrice": "decimal | null",
-"maxPrice": "decimal | null",
-"primaryImageUrl": "string | null",
-"avgRating": "decimal | null",
-"status": "DRAFT|ACTIVE|INACTIVE",
-"auctionStatus": "DRAFT|SCHEDULED|RUNNING|ENDED|SETTLED|FAILED|CANCELLED | null",
-"isOpen": "boolean | null",
-"isSold": "boolean | null"
-}
-],
-"page": "int",
-"pageSize": "int",
-"total": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "productId": "uuid",
+        "name": "string",
+        "brand": "string",
+        "saleType": "REGULAR|AUCTION",
+        "minPrice": "decimal | null",
+        "maxPrice": "decimal | null",
+        "primaryImageUrl": "string | null",
+        "avgRating": "decimal | null",
+        "status": "DRAFT|ACTIVE|INACTIVE",
+        "auctionStatus": "DRAFT|SCHEDULED|RUNNING|ENDED|SETTLED|FAILED|CANCELLED | null",
+        "isOpen": "boolean | null",
+        "isSold": "boolean | null"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Page &lt; 1, pageSize outside 1..100, invalid sortBy/sortDir, or invalid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Page &lt; 1, pageSize outside 1..100, invalid sortBy or sortDir, or invalid UUID format.
 401 UNAUTHORIZED: Provided token is invalid or has expired.</t>
   </si>
   <si>
@@ -3962,7 +4537,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: MinPrice &gt; maxPrice, rating outside 0..5, invalid sortBy, invalid attribute format, or invalid pagination.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Minprice &gt; maxprice, rating outside 0..5, invalid sortBy, invalid attribute format, or invalid pagination.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only sellers or administrators can perform this action.</t>
   </si>
@@ -3988,62 +4563,68 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"product": {
-"productId": "uuid",
-"sellerId": "uuid",
-"categoryId": "uuid",
-"name": "string",
-"description": "string",
-"brand": "string",
-"saleType": "REGULAR|AUCTION",
-"status": "DRAFT|ACTIVE|INACTIVE",
-"statusReason": "SELLER_PAUSED|DISCONTINUED|ADMIN_LOCKED|OTHER | null",
-"specifications": "object",
-"publishedAt": "datetime | null"
-},
-"category": {
-"categoryId": "uuid",
-"parentId": "uuid | null",
-"name": "string",
-"description": "string",
-"level": "int (1..3)",
-"sortOrder": "int",
-"isActive": "boolean"
-},
-"variants": [
-{
-"variantId": "uuid",
-"skuCode": "string",
-"name": "string",
-"price": "decimal | null",
-"status": "ACTIVE|INACTIVE",
-"isDefault": "boolean",
-"attributes": [
-{
-"attrName": "string",
-"attrValue": "string"
-}
-]
-}
-],
-"images": [
-{
-"imageId": "uuid",
-"url": "string",
-"altText": "string",
-"isActive": "boolean",
-"sortOrder": "int",
-"variantId": "uuid | null"
-}
-],
-"rating": {
-"avgRating": "decimal | null",
-"reviewCount": "int"
-}
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "product": {
+      "productId": "uuid",
+      "sellerId": "uuid",
+      "categoryId": "uuid",
+      "name": "string",
+      "description": "string",
+      "brand": "string",
+      "saleType": "REGULAR|AUCTION",
+      "status": "DRAFT|ACTIVE|INACTIVE",
+      "statusReason": "SELLER_PAUSED|DISCONTINUED|ADMIN_LOCKED|OTHER | null",
+      "specifications": "object",
+      "publishedAt": "datetime | null"
+    },
+    "category": {
+      "categoryId": "uuid",
+      "parentId": "uuid | null",
+      "name": "string",
+      "description": "string",
+      "level": "int (1..3)",
+      "sortOrder": "int",
+      "isActive": "boolean"
+    },
+    "variants": [
+      {
+        "variantId": "uuid",
+        "skuCode": "string",
+        "name": "string",
+        "price": "decimal | null",
+        "status": "ACTIVE|INACTIVE",
+        "isDefault": "boolean",
+        "attributes": [
+          {
+            "attrName": "string",
+            "attrValue": "string"
+          }
+        ]
+      }
+    ],
+    "images": [
+      {
+        "imageId": "uuid",
+        "url": "string",
+        "altText": "string",
+        "isActive": "boolean",
+        "sortOrder": "int",
+        "variantId": "uuid | null"
+      }
+    ],
+    "rating": {
+      "avgRating": "decimal | null",
+      "reviewCount": "int"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: ProductId or auctionId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Productid or auctionid is not a valid UUID format.
 404 PRODUCT_NOT_FOUND: Product was not found, has been deleted, or is not accessible.</t>
   </si>
   <si>
@@ -4081,24 +4662,30 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"productId": "uuid",
-"status": "DRAFT",
-"saleType": "REGULAR",
-"variants": [
-{
-"variantId": "uuid",
-"skuCode": "string"
-}
-]
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "productId": "uuid",
+    "status": "DRAFT",
+    "saleType": "REGULAR",
+    "variants": [
+      {
+        "variantId": "uuid",
+        "skuCode": "string"
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 VALIDATION_ERROR: Name is empty, variants missing, price &lt;= 0, no default variant, or duplicate attribute names.
-400 CATEGORY_INVALID: Specified categoryId does not exist, is deactivated, or deleted.
+400 CATEGORY_INVALID: Specified categoryid does not exist, is deactivated, or deleted.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 SELLER_NOT_ALLOWED: Account is not an approved Seller.
-409 SKU_CODE_DUPLICATED: SkuCode already exists on an active variant.
-503 USER_SERVICE_UNAVAILABLE: Failed to verify seller account with User service.</t>
+403 SELLER_NOT_ALLOWED: Account is not an approved seller.
+409 SKU_CODE_DUPLICATED: Skucode already exists on an active variant.
+503 USER_SERVICE_UNAVAILABLE: Failed to verify seller account with user service.</t>
   </si>
   <si>
     <t>CAT-01</t>
@@ -4128,20 +4715,26 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"productId": "uuid",
-"categoryId": "uuid",
-"name": "string",
-"description": "string",
-"brand": "string",
-"saleType": "REGULAR|AUCTION",
-"status": "DRAFT|ACTIVE|INACTIVE",
-"specifications": "object",
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "productId": "uuid",
+    "categoryId": "uuid",
+    "name": "string",
+    "description": "string",
+    "brand": "string",
+    "saleType": "REGULAR|AUCTION",
+    "status": "DRAFT|ACTIVE|INACTIVE",
+    "specifications": "object",
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Empty update payload, name is empty, or invalid productId UUID format.
-400 CATEGORY_INVALID: New categoryId does not exist, is deactivated, or deleted.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Empty update payload, name is empty, or invalid productid UUID format.
+400 CATEGORY_INVALID: New categoryid does not exist, is deactivated, or deleted.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.</t>
@@ -4170,11 +4763,11 @@
     <t>204 No Content</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: ProductId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Productid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.
-409 PRODUCT_HAS_ORDER: Product has variants with associated orders. Please deactivate instead.
+409 PRODUCT_HAS_ORDER: Product has variants with associated orders, please deactivate instead.
 409 PRODUCT_IN_AUCTION: Product is in an active auction and cannot be modified.</t>
   </si>
   <si>
@@ -4204,24 +4797,38 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"items": [
-{
-"imageId": "uuid",
-"url": "string",
-"isActive": "boolean",
-"sortOrder": "int"
-}
-]
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "items": [
+      {
+        "imageId": "uuid",
+        "url": "string",
+        "isActive": "boolean",
+        "sortOrder": "int"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Files list is empty, variantId does not belong to product, or invalid productId.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Files list is empty, variantid does not belong to product, or invalid productid.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.
 409 IMAGE_LIMIT_EXCEEDED: Total images for this product cannot exceed 5.
 413 FILE_TOO_LARGE: File size exceeds the maximum allowed limit.
-415 UNSUPPORTED_MEDIA_TYPE: Unsupported media type. Only JPG, PNG, and WEBP formats are allowed.
+415 UNSUPPORTED_MEDIA_TYPE: Unsupported media type, only JPG, PNG, and WEBP formats are allowed.
 503 STORAGE_UNAVAILABLE: Failed to upload file to object storage service.</t>
   </si>
   <si>
@@ -4243,20 +4850,34 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"imageId": "uuid",
-"url": "string",
-"altText": "string",
-"isActive": "boolean",
-"sortOrder": "int",
-"variantId": "uuid | null"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "imageId": "uuid",
+        "url": "string",
+        "altText": "string",
+        "isActive": "boolean",
+        "sortOrder": "int",
+        "variantId": "uuid | null"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: ProductId or variantId is not a valid UUID, or variant does not belong to product.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Productid or variantid is not a valid UUID, or variant does not belong to product.
 404 PRODUCT_NOT_FOUND: Product was not found, has been deleted, or is not active.</t>
   </si>
   <si>
@@ -4296,13 +4917,19 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"productId": "uuid",
-"avgRating": "decimal | null",
-"reviewCount": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "productId": "uuid",
+    "avgRating": "decimal | null",
+    "reviewCount": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: ProductId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Productid is not a valid UUID format.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.</t>
   </si>
   <si>
@@ -4328,26 +4955,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"rating": {
-"avgRating": "decimal | null",
-"reviewCount": "int"
-},
-"items": [
-{
-"reviewId": "uuid",
-"rating": "int (1..5)",
-"comment": "string",
-"createdAt": "datetime",
-"reviewerName": "string | null"
-}
-],
-"page": "int",
-"pageSize": "int",
-"total": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "reviewId": "uuid",
+        "rating": "int (1..5)",
+        "comment": "string",
+        "createdAt": "datetime",
+        "reviewerName": "string | null"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination, rating outside 1..5, invalid sortBy, or invalid productId format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination, rating outside 1..5, invalid sortBy, or invalid productid format.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.</t>
   </si>
   <si>
@@ -4378,16 +5012,22 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"productId": "uuid",
-"status": "DRAFT|ACTIVE|INACTIVE",
-"statusReason": "string | null",
-"publishedAt": "datetime | null"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "productId": "uuid",
+    "status": "DRAFT|ACTIVE|INACTIVE",
+    "statusReason": "string | null",
+    "publishedAt": "datetime | null"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid status, missing statusReason for INACTIVE, or unexpected statusReason.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid status, missing statusreason for inactive, or unexpected statusreason.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 FORBIDDEN: You are not the product owner, or product is locked by admin (only Admin can unlock).
+403 FORBIDDEN: You are not the product owner, or product is locked by admin (only admin can unlock).
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.
 409 PRODUCT_NOT_PUBLISHABLE: Cannot activate product without active variants or valid variant prices.
 409 PRODUCT_IN_AUCTION: Cannot hide product while it is in an active auction.</t>
@@ -4419,21 +5059,35 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"skuId": "uuid",
-"addedQuantity": "int",
-"stockQuantity": "int"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "skuId": "uuid",
+        "addedQuantity": "int",
+        "stockQuantity": "int"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Items list is empty, quantity &lt;= 0, exceeds 100 SkuIds, or duplicate SkuIds.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Items list is empty, quantity &lt;= 0, exceeds 100 SKUs, or duplicate SKUs.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 FORBIDDEN: One or more SkuIds do not belong to the calling seller products.
-404 SKU_NOT_FOUND: One or more SkuIds do not exist or have been deleted.
-503 CATALOG_UNAVAILABLE: Fulfillment service failed to communicate with Catalog service.</t>
+403 FORBIDDEN: One or more SKUs do not belong to the calling seller products.
+404 SKU_NOT_FOUND: One or more SKUs do not exist or have been deleted.
+503 CATALOG_UNAVAILABLE: Fulfillment service failed to communicate with catalog service.</t>
   </si>
   <si>
     <t>FUL-02 + CAT-24</t>
@@ -4468,17 +5122,23 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"variantId": "uuid",
-"skuCode": "string",
-"status": "ACTIVE|INACTIVE"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "variantId": "uuid",
+    "skuCode": "string",
+    "status": "ACTIVE|INACTIVE"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Price must be &gt; 0, attribute names mismatch with existing variants, or invalid productId.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Price must be &gt; 0, attribute names mismatch with existing variants, or invalid productid.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 PRODUCT_NOT_FOUND: Product was not found or has been deleted.
-409 SKU_CODE_DUPLICATED: SkuCode already exists on an active variant.
+409 SKU_CODE_DUPLICATED: Skucode already exists on an active variant.
 409 AUCTION_PRODUCT_SINGLE_VARIANT: Auction products cannot have additional variants.</t>
   </si>
   <si>
@@ -4499,12 +5159,12 @@
 {"variantId": "uuid"}</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: VariantId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Variantid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 VARIANT_NOT_FOUND: Variant was not found or has been deleted.
 409 LAST_VARIANT: Cannot delete the last remaining variant of a product.
-409 VARIANT_HAS_ORDER: Variant has existing orders. Please change status to INACTIVE instead.</t>
+409 VARIANT_HAS_ORDER: Variant has existing orders, please change status to inactive instead.</t>
   </si>
   <si>
     <t>CAT-11</t>
@@ -4535,25 +5195,31 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"variantId": "uuid",
-"productId": "uuid",
-"skuCode": "string",
-"name": "string",
-"price": "decimal | null",
-"currency": "string",
-"status": "ACTIVE|INACTIVE",
-"attributes": [
-{
-"attrName": "string",
-"attrValue": "string"
-}
-],
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "variantId": "uuid",
+    "productId": "uuid",
+    "skuCode": "string",
+    "name": "string",
+    "price": "decimal | null",
+    "currency": "string",
+    "status": "ACTIVE|INACTIVE",
+    "attributes": [
+      {
+        "attrName": "string",
+        "attrValue": "string"
+      }
+    ],
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Empty update payload, invalid price for saleType, or attribute names mismatch.
-400 PRICE_REQUIRED: Active REGULAR product must have a valid price.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Empty update payload, invalid price for saletype, or attribute names mismatch.
+400 PRICE_REQUIRED: Active regular product must have a valid price.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 VARIANT_NOT_FOUND: Variant was not found or has been deleted.</t>
@@ -4567,33 +5233,39 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"variantId": "uuid",
-"productId": "uuid",
-"skuCode": "string",
-"name": "string",
-"price": "decimal | null",
-"currency": "string",
-"status": "ACTIVE|INACTIVE",
-"statusReason": "OUT_OF_STOCK|DISCONTINUED|OTHER | null",
-"isDefault": "boolean",
-"hasOrder": "boolean",
-"attributes": [
-{
-"attrName": "string",
-"attrValue": "string"
-}
-],
-"images": [
-{
-"imageId": "uuid",
-"url": "string",
-"isActive": "boolean"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "variantId": "uuid",
+    "productId": "uuid",
+    "skuCode": "string",
+    "name": "string",
+    "price": "decimal | null",
+    "currency": "string",
+    "status": "ACTIVE|INACTIVE",
+    "statusReason": "OUT_OF_STOCK|DISCONTINUED|OTHER | null",
+    "isDefault": "boolean",
+    "hasOrder": "boolean",
+    "attributes": [
+      {
+        "attrName": "string",
+        "attrValue": "string"
+      }
+    ],
+    "images": [
+      {
+        "imageId": "uuid",
+        "url": "string",
+        "isActive": "boolean"
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: VariantId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Variantid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the owner of this product and not an administrator.
 404 VARIANT_NOT_FOUND: Variant was not found or has been deleted.</t>
@@ -4626,17 +5298,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"skuId": "uuid",
-"addedQuantity": "int",
-"stockQuantity": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "skuId": "uuid",
+    "addedQuantity": "int",
+    "stockQuantity": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Quantity must be greater than zero or invalid variantId format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Quantity must be greater than zero or invalid variantid format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Variant does not belong to a product owned by the calling seller.
 404 VARIANT_NOT_FOUND: Variant was not found or has been deleted.
-503 CATALOG_UNAVAILABLE: Fulfillment service failed to communicate with Catalog service.</t>
+503 CATALOG_UNAVAILABLE: Fulfillment service failed to communicate with catalog service.</t>
   </si>
   <si>
     <t>FUL-02 + CAT-23</t>
@@ -4658,19 +5336,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"categoryId": "uuid",
-"name": "string",
-"level": "int (1..3)",
-"sortOrder": "int",
-"children": "[ ... cùng cấu trúc, chỉ có khi Tree = true ]"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "categoryId": "uuid",
+        "name": "string",
+        "level": "int (1..3)",
+        "sortOrder": "int",
+        "children": "[ ... cùng cấu trúc, chỉ có khi Tree = true ]"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid parentId UUID format or tree parameter must be boolean.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid parentid UUID format or tree parameter must be boolean.
 404 PARENT_NOT_FOUND: Parent category was not found or has been deleted.</t>
   </si>
   <si>
@@ -4695,12 +5387,18 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"categoryId": "uuid",
-"level": "int (1..3)"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "categoryId": "uuid",
+    "level": "int (1..3)"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Category name is empty or parentId is not a valid UUID.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Category name is empty or parentid is not a valid UUID.
 400 CATEGORY_LEVEL_EXCEEDED: Category hierarchy level exceeds maximum limit of 3.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only administrators can perform this action.
@@ -4735,14 +5433,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"categoryId": "uuid",
-"parentId": "uuid | null",
-"name": "string",
-"description": "string",
-"level": "int (1..3)",
-"sortOrder": "int",
-"isActive": "boolean",
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "categoryId": "uuid",
+    "parentId": "uuid | null",
+    "name": "string",
+    "description": "string",
+    "level": "int (1..3)",
+    "sortOrder": "int",
+    "isActive": "boolean",
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -4770,7 +5474,7 @@
 {"categoryId": "uuid"}</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: CategoryId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Categoryid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only administrators can perform this action.
 404 CATEGORY_NOT_FOUND: Category was not found or has been deleted.
@@ -4790,27 +5494,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"category": {
-"categoryId": "uuid",
-"parentId": "uuid | null",
-"name": "string",
-"description": "string",
-"level": "int (1..3)",
-"sortOrder": "int",
-"isActive": "boolean"
-},
-"parent": "{ CategoryId, Name, Level } | null (null nếu là danh mục gốc)",
-"children": [
-{
-"categoryId": "uuid",
-"name": "string",
-"level": "int"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "category": {
+      "categoryId": "uuid",
+      "parentId": "uuid | null",
+      "name": "string",
+      "description": "string",
+      "level": "int (1..3)",
+      "sortOrder": "int",
+      "isActive": "boolean"
+    },
+    "parent": "{ CategoryId, Name, Level } | null (null nếu là danh mục gốc)",
+    "children": [
+      {
+        "categoryId": "uuid",
+        "name": "string",
+        "level": "int"
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: CategoryId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Categoryid is not a valid UUID format.
 404 CATEGORY_NOT_FOUND: Category was not found or has been deleted.</t>
   </si>
   <si>
@@ -4852,22 +5562,28 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"productId": "uuid",
-"status": "DRAFT",
-"saleType": "AUCTION",
-"variant": {
-"variantId": "uuid",
-"skuCode": "string"
-}
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "productId": "uuid",
+    "status": "DRAFT",
+    "saleType": "AUCTION",
+    "variant": {
+      "variantId": "uuid",
+      "skuCode": "string"
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">400 VALIDATION_ERROR: Name is empty, variant definition invalid, or unexpected price field for auction product.
-400 CATEGORY_INVALID: Specified categoryId does not exist, is deactivated, or deleted.
+400 CATEGORY_INVALID: Specified categoryid does not exist, is deactivated, or deleted.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 SELLER_NOT_ALLOWED: Account is not an approved Seller or has insufficient reputation for auctions.
-409 SKU_CODE_DUPLICATED: SkuCode already exists on an active variant.
-503 USER_SERVICE_UNAVAILABLE: Failed to verify seller account with User service.</t>
+403 SELLER_NOT_ALLOWED: Account is not an approved seller or has insufficient reputation for auctions.
+409 SKU_CODE_DUPLICATED: Skucode already exists on an active variant.
+503 USER_SERVICE_UNAVAILABLE: Failed to verify seller account with user service.</t>
   </si>
   <si>
     <t>CAT-43 (mới)</t>
@@ -4902,7 +5618,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination, sortBy parameter, or invalid categoryId format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination, sortBy parameter, or invalid categoryid format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only sellers or administrators can perform this action.</t>
   </si>
@@ -4949,23 +5665,29 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auction": {
-"auctionId": "uuid",
-"status": "DRAFT|SCHEDULED|RUNNING|ENDED|SETTLED|FAILED|CANCELLED",
-"startingPriceAmount": "number",
-"bidStepAmount": "number",
-"currentPriceAmount": "number | null",
-"currentLeadingBidderMasked": "string | null",
-"bidCount": "int",
-"startsAt": "datetime",
-"endsAt": "datetime",
-"extensionCount": "int"
-},
-"product": "(như dòng 111, CAT-05: Product, Category, Variants, Images, Rating)"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auction": {
+      "auctionId": "uuid",
+      "status": "DRAFT|SCHEDULED|RUNNING|ENDED|SETTLED|FAILED|CANCELLED",
+      "startingPriceAmount": "number",
+      "bidStepAmount": "number",
+      "currentPriceAmount": "number | null",
+      "currentLeadingBidderMasked": "string | null",
+      "bidCount": "int",
+      "startsAt": "datetime",
+      "endsAt": "datetime",
+      "extensionCount": "int"
+    },
+    "product": "(như dòng 111, CAT-05: Product, Category, Variants, Images, Rating)"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the seller of this auction and not an administrator.
 404 AUCTION_NOT_FOUND: Auction was not found.
@@ -4979,7 +5701,7 @@
     <t>AUC-35</t>
   </si>
   <si>
-    <t>F3. đấu giá</t>
+    <t>F3. đấu giá.</t>
   </si>
   <si>
     <t>/api/v1/auctions</t>
@@ -4998,24 +5720,40 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"auctionId": "UUID", "productId": "UUID", "skuId": "UUID", "sellerId": "UUID",
-"productName": "string",
-"primaryImageUrl": "string | null",
-"status": "AuctionStatus",
-"startPriceAmount": "number",
-"currentPriceAmount": "number | null",
-"bidCount": "int",
-"scheduledStartAt": "datetime",
-"scheduledEndAt": "datetime"
-}
-],
-"total": "int", "page": "int", "pageSize": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "auctionId": "UUID",
+        "productId": "UUID",
+        "skuId": "UUID",
+        "sellerId": "UUID",
+        "productName": "string",
+        "primaryImageUrl": "string | null",
+        "status": "AuctionStatus",
+        "startPriceAmount": "number",
+        "currentPriceAmount": "number | null",
+        "bidCount": "int",
+        "scheduledStartAt": "datetime",
+        "scheduledEndAt": "datetime"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid AuctionStatus enum.</t>
+    <t>400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid auctionstatus enum.</t>
   </si>
   <si>
     <t>AUC-01</t>
@@ -5036,32 +5774,46 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID", "productId": "UUID", "skuId": "UUID", "sellerId": "UUID",
-"productName": "string",
-"description": "string | null",
-"images": [ { "url": "string", "isPrimary": "boolean" } ],
-"specifications": "object | null",
-"status": "AuctionStatus",
-"startPriceAmount": "number",
-"bidStepAmount": "number",
-"currentPriceAmount": "number | null",
-"bidCount": "int",
-"leadingBidderDisplayName": "string | null",
-"scheduledStartAt": "datetime",
-"originalEndAt": "datetime",
-"scheduledEndAt": "datetime",
-"startedAt": "datetime | null",
-"endedAt": "datetime | null",
-"extensionCount": "int",
-"maxExtensionCount": "int",
-"antiSnipingExtensionMinutes": "int",
-"minReputationToBid": "int",
-"recreatedFromAuctionId": "UUID | null",
-"createdAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "productId": "UUID",
+    "skuId": "UUID",
+    "sellerId": "UUID",
+    "productName": "string",
+    "description": "string | null",
+    "images": [
+      {
+        "url": "string",
+        "isPrimary": "boolean"
+      }
+    ],
+    "specifications": "object | null",
+    "status": "AuctionStatus",
+    "startPriceAmount": "number",
+    "bidStepAmount": "number",
+    "currentPriceAmount": "number | null",
+    "bidCount": "int",
+    "leadingBidderDisplayName": "string | null",
+    "scheduledStartAt": "datetime",
+    "originalEndAt": "datetime",
+    "scheduledEndAt": "datetime",
+    "startedAt": "datetime | null",
+    "endedAt": "datetime | null",
+    "extensionCount": "int",
+    "maxExtensionCount": "int",
+    "antiSnipingExtensionMinutes": "int",
+    "minReputationToBid": "int",
+    "recreatedFromAuctionId": "UUID | null",
+    "createdAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format.
 404 AUCTION_NOT_FOUND: Auction was not found.</t>
   </si>
   <si>
@@ -5084,17 +5836,25 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"auctionId": "UUID", "productId": "UUID", "skuId": "UUID",
-"productName": "string",
-"status": "SCHEDULED",
-"startPriceAmount": "number",
-"bidStepAmount": "number",
-"scheduledStartAt": "datetime",
-"scheduledEndAt": "datetime",
-"minReputationToBid": "int",
-"antiSnipingExtensionMinutes": "int",
-"maxExtensionCount": "int",
-"createdAt": "datetime"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "auctionId": "UUID",
+    "productId": "UUID",
+    "skuId": "UUID",
+    "productName": "string",
+    "status": "SCHEDULED",
+    "startPriceAmount": "number",
+    "bidStepAmount": "number",
+    "scheduledStartAt": "datetime",
+    "scheduledEndAt": "datetime",
+    "minReputationToBid": "int",
+    "antiSnipingExtensionMinutes": "int",
+    "maxExtensionCount": "int",
+    "createdAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5133,17 +5893,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"status": "SCHEDULED",
-"startPriceAmount": "number",
-"bidStepAmount": "number",
-"scheduledStartAt": "datetime",
-"scheduledEndAt": "datetime",
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "status": "SCHEDULED",
+    "startPriceAmount": "number",
+    "bidStepAmount": "number",
+    "scheduledStartAt": "datetime",
+    "scheduledEndAt": "datetime",
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionId, empty payload, or invalid pricing/scheduling values.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionid, empty payload, or invalid pricing/scheduling values.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the seller of this auction.
 404 AUCTION_NOT_FOUND: Auction was not found.
@@ -5168,19 +5934,25 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"auctionId": "UUID",
-"fromStatus": "AuctionStatus",
-"status": "CANCELLED",
-"reason": "string | null",
-"cancelledAt": "datetime"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "auctionId": "UUID",
+    "fromStatus": "AuctionStatus",
+    "status": "CANCELLED",
+    "reason": "string | null",
+    "cancelledAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format or cancellation reason is empty.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format or cancellation reason is empty.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the seller of this auction.
 404 AUCTION_NOT_FOUND: Auction was not found.
-409 AUCTION_HAS_BIDS: Auction already has bids. Only an administrator can cancel it.
+409 AUCTION_HAS_BIDS: Auction already has bids, only an administrator can cancel it.
 409 CONCURRENT_UPDATE: Auction status was modified concurrently by another operation.
 422 INVALID_STATE_TRANSITION: Auction status is invalid for cancellation.</t>
   </si>
@@ -5207,26 +5979,33 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"auctionId": "UUID (phiên mới)",
-"recreatedFromAuctionId": "UUID",
-"productId": "UUID", "skuId": "UUID",
-"status": "SCHEDULED",
-"startPriceAmount": "number",
-"bidStepAmount": "number",
-"scheduledStartAt": "datetime",
-"scheduledEndAt": "datetime",
-"createdAt": "datetime"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "auctionId": "UUID (phiên mới)",
+    "recreatedFromAuctionId": "UUID",
+    "productId": "UUID",
+    "skuId": "UUID",
+    "status": "SCHEDULED",
+    "startPriceAmount": "number",
+    "bidStepAmount": "number",
+    "scheduledStartAt": "datetime",
+    "scheduledEndAt": "datetime",
+    "createdAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionId, start price &lt; 0, bid step &lt;= 0, start time in past, or invalid schedule.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionid, start price &lt; 0, bid step &lt;= 0, start time in past, or invalid schedule.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Previous auction does not belong to the calling seller.
 403 SELLER_NOT_ELIGIBLE: Reputation score is below the auction hosting threshold (minimum 50).
 404 AUCTION_NOT_FOUND: Previous auction was not found.
 409 PRODUCT_ALREADY_IN_AUCTION: Product already has an ongoing or scheduled auction.
 409 INVENTORY_UNAVAILABLE: Inventory stock hold failed.
-422 INVALID_RECREATE_SOURCE: Previous auction is not in FAILED status.
+422 INVALID_RECREATE_SOURCE: Previous auction is not in failed status.
 422 PRODUCT_NOT_ELIGIBLE: Product is no longer eligible.
 422 INVALID_SCHEDULE: Start time cannot exceed 30 days or duration cannot be under 1 hour.
 503 USER_SERVICE_UNAVAILABLE: User service is currently unavailable.</t>
@@ -5249,23 +6028,36 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"items": [
-{
-"id": "UUID",
-"fromStatus": "AuctionStatus | null",
-"toStatus": "AuctionStatus",
-"reason": "string | null",
-"changedBy": "UUID | null",
-"changedAt": "datetime"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "UUID",
+        "fromStatus": "AuctionStatus | null",
+        "toStatus": "AuctionStatus",
+        "reason": "string | null",
+        "changedBy": "UUID | null",
+        "changedAt": "datetime"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format or invalid pagination parameters.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format or invalid pagination parameters.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 FORBIDDEN: Administrator or Staff privileges are required.
+403 FORBIDDEN: Administrator or staff privileges are required.
 404 AUCTION_NOT_FOUND: Auction was not found.</t>
   </si>
   <si>
@@ -5292,25 +6084,40 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"auctionId": "UUID", "productId": "UUID", "skuId": "UUID",
-"productName": "string",
-"primaryImageUrl": "string | null",
-"status": "AuctionStatus",
-"startPriceAmount": "number",
-"currentPriceAmount": "number | null",
-"bidCount": "int",
-"scheduledStartAt": "datetime",
-"scheduledEndAt": "datetime",
-"createdAt": "datetime"
-}
-],
-"total": "int", "page": "int", "pageSize": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "auctionId": "UUID",
+        "productId": "UUID",
+        "skuId": "UUID",
+        "productName": "string",
+        "primaryImageUrl": "string | null",
+        "status": "AuctionStatus",
+        "startPriceAmount": "number",
+        "currentPriceAmount": "number | null",
+        "bidCount": "int",
+        "scheduledStartAt": "datetime",
+        "scheduledEndAt": "datetime",
+        "createdAt": "datetime"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid AuctionStatus enum.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid auctionstatus enum.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only registered sellers can perform this action.</t>
   </si>
@@ -5339,18 +6146,24 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"auctionId": "UUID",
-"fromStatus": "AuctionStatus",
-"status": "CANCELLED",
-"reason": "string",
-"cancelledBy": "UUID",
-"cancelledAt": "datetime"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "auctionId": "UUID",
+    "fromStatus": "AuctionStatus",
+    "status": "CANCELLED",
+    "reason": "string",
+    "cancelledBy": "UUID",
+    "cancelledAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format or cancellation reason is empty.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format or cancellation reason is empty.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 FORBIDDEN: Administrator privileges required. Support Staff cannot perform this action.
+403 FORBIDDEN: Administrator privileges required, support staff cannot perform this action.
 404 AUCTION_NOT_FOUND: Auction was not found.
 409 CONCURRENT_UPDATE: Auction status was modified concurrently by another operation.
 422 INVALID_STATE_TRANSITION: Auction status is invalid for cancellation (ended auctions cannot be cancelled).</t>
@@ -5378,18 +6191,24 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"sagaType": "string",
-"currentState": "string",
-"stateData": "object",
-"createdAt": "datetime",
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "sagaType": "string",
+    "currentState": "string",
+    "stateData": "object",
+    "createdAt": "datetime",
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
-403 FORBIDDEN: Administrator or Staff privileges are required.
+403 FORBIDDEN: Administrator or staff privileges are required.
 404 AUCTION_NOT_FOUND: Auction was not found or has no winning saga.</t>
   </si>
   <si>
@@ -5404,16 +6223,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"configKey": "string",
-"configValue": "json",
-"description": "string | null",
-"version": "int",
-"updatedBy": "UUID | null",
-"updatedAt": "datetime"
-}
-]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "configKey": "string",
+        "configValue": "json",
+        "description": "string | null",
+        "version": "int",
+        "updatedBy": "UUID | null",
+        "updatedAt": "datetime"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5448,14 +6281,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"configKey": "string",
-"configValue": "json",
-"description": "string | null",
-"version": "int",
-"isActive": "boolean",
-"updatedBy": "UUID | null",
-"createdAt": "datetime",
-"updatedAt": "datetime"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "configKey": "string",
+    "configValue": "json",
+    "description": "string | null",
+    "version": "int",
+    "isActive": "boolean",
+    "updatedBy": "UUID | null",
+    "createdAt": "datetime",
+    "updatedAt": "datetime"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5463,7 +6302,7 @@
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: Only administrators can perform this action.
 404 NOT_FOUND: Configuration key was not found.
-409 CONFLICT: Update conflict. Only one active record is permitted per key.</t>
+409 CONFLICT: Update conflict, only one active record is permitted per key.</t>
   </si>
   <si>
     <t>AUC-17</t>
@@ -5483,25 +6322,31 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-"bidId": "UUID",
-"auctionId": "UUID",
-"bidSeq": "int",
-"amount": "number",
-"placedAt": "datetime",
-"currentPriceAmount": "number",
-"bidCount": "int",
-"scheduledEndAt": "datetime",
-"extensionCount": "int"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "bidId": "UUID",
+    "auctionId": "UUID",
+    "bidSeq": "int",
+    "amount": "number",
+    "placedAt": "datetime",
+    "currentPriceAmount": "number",
+    "bidCount": "int",
+    "scheduledEndAt": "datetime",
+    "extensionCount": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionId, missing Idempotency-Key/If-Match, or invalid bid amount.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid auctionid, missing Idempotency-Key or If-Match header, or invalid bid amount.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 BIDDER_NOT_ELIGIBLE: Reputation score is below bidding threshold (minimum 40) or account is locked.
 404 AUCTION_NOT_FOUND: Auction was not found.
-409 CONCURRENT_UPDATE: Concurrent update detected (rowVersion mismatch or earlier bid).
+409 CONCURRENT_UPDATE: Concurrent update detected (rowversion mismatch or earlier bid).
 410 AUCTION_ENDED: Auction has ended or scheduled end time has passed.
-422 AUCTION_NOT_RUNNING: Auction is not in RUNNING status.
+422 AUCTION_NOT_RUNNING: Auction is not in running status.
 422 BID_TOO_LOW: Bid amount is below the minimum required bid increment.
 422 IDEMPOTENCY_KEY_REUSED: Idempotency key reused with different request payload.
 503 USER_SERVICE_UNAVAILABLE: User service is currently unavailable.</t>
@@ -5530,24 +6375,37 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"bidId": "UUID",
-"sequenceNo": "int",
-"bidderId": "UUID",
-"bidderDisplayName": "string",
-"amount": "number",
-"placedAt": "datetime",
-"isOutbid": "boolean",
-"isWinning": "boolean",
-"isInvalidated": "boolean"
-}
-],
-"total": "int", "page": "int", "pageSize": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "bidId": "UUID",
+        "sequenceNo": "int",
+        "bidderId": "UUID",
+        "bidderDisplayName": "string",
+        "amount": "number",
+        "placedAt": "datetime",
+        "isOutbid": "boolean",
+        "isWinning": "boolean",
+        "isInvalidated": "boolean"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format or invalid pagination parameters.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format or invalid pagination parameters.
 404 AUCTION_NOT_FOUND: Auction was not found.</t>
   </si>
   <si>
@@ -5565,24 +6423,38 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"items": [
-{
-"auctionId": "UUID", "productId": "UUID",
-"productName": "string",
-"primaryImageUrl": "string | null",
-"auctionStatus": "AuctionStatus",
-"myHighestBidAmount": "number",
-"currentPriceAmount": "number | null",
-"isLeading": "boolean",
-"endsAt": "datetime",
-"lastBidAt": "datetime"
-}
-],
-"total": "int", "page": "int", "pageSize": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "auctionId": "UUID",
+        "productId": "UUID",
+        "productName": "string",
+        "primaryImageUrl": "string | null",
+        "auctionStatus": "AuctionStatus",
+        "myHighestBidAmount": "number",
+        "currentPriceAmount": "number | null",
+        "isLeading": "boolean",
+        "endsAt": "datetime",
+        "lastBidAt": "datetime"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
+    }
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid AuctionStatus enum.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Invalid pagination parameters or status is not a valid auctionstatus enum.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.</t>
   </si>
   <si>
@@ -5597,22 +6469,28 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"status": "AuctionStatus",
-"hasWinner": "boolean",
-"winnerId": "UUID | null",
-"winnerDisplayName": "string | null",
-"sellerId": "UUID",
-"winningBidId": "UUID | null",
-"finalPriceAmount": "number | null",
-"determinedAt": "datetime",
-"orderId": "UUID | null",
-"paymentDeadlineAt": "datetime | null",
-"paidAt": "datetime | null",
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "status": "AuctionStatus",
+    "hasWinner": "boolean",
+    "winnerId": "UUID | null",
+    "winnerDisplayName": "string | null",
+    "sellerId": "UUID",
+    "winningBidId": "UUID | null",
+    "finalPriceAmount": "number | null",
+    "determinedAt": "datetime",
+    "orderId": "UUID | null",
+    "paymentDeadlineAt": "datetime | null",
+    "paidAt": "datetime | null"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format.
 401 UNAUTHORIZED: Token is missing, expired, or invalid.
 403 FORBIDDEN: You are not the winner, seller, or administrator of this auction.
 404 AUCTION_NOT_FOUND: Auction was not found.</t>
@@ -5638,10 +6516,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"status": "",
-"paymentDeadlineAt": "datetime | null",
-"isWithinDeadline": "boolean"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "status": "",
+    "paymentDeadlineAt": "datetime | null",
+    "isWithinDeadline": "boolean"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5664,16 +6548,22 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"productId": "UUID",
-"auctionId": "UUID | null",
-"status": "",
-"isOpen": "boolean",
-"isSold": "boolean"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "productId": "UUID",
+    "auctionId": "UUID | null",
+    "status": "",
+    "isOpen": "boolean",
+    "isSold": "boolean"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: ProductId is not a valid UUID format.
-403 FORBIDDEN: Only internal Catalog service can call this endpoint.</t>
+    <t xml:space="preserve">400 VALIDATION_ERROR: Productid is not a valid UUID format.
+403 FORBIDDEN: Only internal catalog service can call this endpoint.</t>
   </si>
   <si>
     <t>/internal/v1/auctions/{auctionId}/summary</t>
@@ -5694,28 +6584,34 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-"auctionId": "UUID",
-"productId": "UUID",
-"sellerId": "UUID",
-"status": ",
-"startingPriceAmount": "number",
-"bidStepAmount": "number",
-"currentPriceAmount": "number | null",
-"currentLeadingBidderId": "UUID | null",
-"currentLeadingBidderMasked": "string | null",
-"bidCount": "int",
-"startsAt": "datetime",
-"endsAt": "datetime",
-"extensionCount": "int"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "auctionId": "UUID",
+    "productId": "UUID",
+    "sellerId": "UUID",
+    "status": "AuctionStatus",
+    "startingPriceAmount": "number",
+    "bidStepAmount": "number",
+    "currentPriceAmount": "number | null",
+    "currentLeadingBidderId": "UUID | null",
+    "currentLeadingBidderMasked": "string | null",
+    "bidCount": "int",
+    "startsAt": "datetime",
+    "endsAt": "datetime",
+    "extensionCount": "int"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">400 VALIDATION_ERROR: AuctionId is not a valid UUID format.
-403 FORBIDDEN: Only internal Catalog service can call this endpoint.
+    <t xml:space="preserve">400 VALIDATION_ERROR: Auctionid is not a valid UUID format.
+403 FORBIDDEN: Only internal catalog service can call this endpoint.
 404 AUCTION_NOT_FOUND: Auction was not found.</t>
   </si>
   <si>
-    <t>F5. thanh toán</t>
+    <t>F5. thanh toán.</t>
   </si>
   <si>
     <t>/api/v1/wallets/me</t>
@@ -5726,14 +6622,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "walletId": "uuid",
-  "userId": "uuid",
-  "balance": 1500000.00,
-  "lockedBalance": 200000.00,
-  "availableBalance": 1300000.00,
-  "currency": "VND",
-  "status": "ACTIVE",
-  "updatedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "walletId": "uuid",
+    "userId": "uuid",
+    "balance": 1500000.0,
+    "lockedBalance": 200000.0,
+    "availableBalance": 1300000.0,
+    "currency": "VND",
+    "status": "ACTIVE",
+    "updatedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5765,10 +6667,16 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "topupId": "uuid",
-  "paymentUrl": "https://sandbox.vnpayment.vn/paymentv2/vpcpay.html?vnp_Amount=50000000...",
-  "txnRef": "TOPUP-20261026-1234",
-  "expiresIn": 900
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "topupId": "uuid",
+    "paymentUrl": "https://sandbox.vnpayment.vn/paymentv2/vpcpay.html?vnp_Amount=50000000...",
+    "txnRef": "TOPUP-20261026-1234",
+    "expiresIn": 900
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5837,12 +6745,18 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "transactionId": "uuid",
-  "orderId": "uuid",
-  "amount": 480000,
-  "paymentUrl": "https://sandbox.vnpayment.vn/paymentv2/vpcpay.html?vnp_Amount=48000000...",
-  "status": "PENDING",
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "transactionId": "uuid",
+    "orderId": "uuid",
+    "amount": 480000,
+    "paymentUrl": "https://sandbox.vnpayment.vn/paymentv2/vpcpay.html?vnp_Amount=48000000...",
+    "status": "PENDING",
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5876,11 +6790,17 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "withdrawalId": "uuid",
-  "amount": 200000,
-  "fee": 0,
-  "status": "PENDING",
-  "requestedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "withdrawalId": "uuid",
+    "amount": 200000,
+    "fee": 0,
+    "status": "PENDING",
+    "requestedAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5916,10 +6836,16 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "withdrawalId": "uuid",
-  "status": "APPROVED",
-  "processedAt": "2026-10-26T00:00:00Z",
-  "transactionId": "uuid"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "withdrawalId": "uuid",
+    "status": "APPROVED",
+    "processedAt": "2026-10-26T00:00:00Z",
+    "transactionId": "uuid"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -5954,20 +6880,31 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "id": "uuid",
-      "type": "PAYMENT",
-      "amount": -480000,
-      "balanceAfter": 1020000,
-      "status": "SUCCESS",
-      "note": "Payment for order #SUB-01",
-      "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "type": "PAYMENT",
+        "amount": -480000,
+        "balanceAfter": 1020000,
+        "status": "SUCCESS",
+        "note": "Payment for order #SUB-01",
+        "createdAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
     }
-  ],
-  "total": 1,
-  "page": 1,
-  "limit": 20
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6002,11 +6939,17 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "adjustmentId": "uuid",
-  "walletId": "uuid",
-  "amount": 50000,
-  "balanceAfter": 1070000,
-  "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "adjustmentId": "uuid",
+    "walletId": "uuid",
+    "amount": 50000,
+    "balanceAfter": 1070000,
+    "createdAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6038,11 +6981,17 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "deviceId": "uuid",
-  "userId": "uuid",
-  "platform": "WEB|IOS|ANDROID",
-  "isActive": true,
-  "lastSeenAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "deviceId": "uuid",
+    "userId": "uuid",
+    "platform": "WEB|IOS|ANDROID",
+    "isActive": true,
+    "lastSeenAt": "2026-10-26T00:00:00Z"
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6082,14 +7031,28 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "notificationType": "ORDER_PAID|AUCTION_OUTBID|PROMOTION",
-      "channelCode": "EMAIL|PUSH|IN_APP",
-      "isEnabled": true,
-      "isMandatory": true
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "notificationType": "ORDER_PAID|AUCTION_OUTBID|PROMOTION",
+        "channelCode": "EMAIL|PUSH|IN_APP",
+        "isEnabled": true,
+        "isMandatory": true
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6120,14 +7083,20 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "updatedCount": 1,
-  "preferences": [
-    {
-      "notificationType": "ORDER_PAID",
-      "channelCode": "EMAIL",
-      "isEnabled": true
-    }
-  ]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "updatedCount": 1,
+    "preferences": [
+      {
+        "notificationType": "ORDER_PAID",
+        "channelCode": "EMAIL",
+        "isEnabled": true
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6160,23 +7129,35 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "unreadCount": 3,
-  "totalCount": 10,
-  "items": [
-    {
-      "id": "uuid",
-      "notificationType": "ORDER_PAID",
-      "title": "Don hang #SUB-01 da duoc thanh toan",
-      "body": "Don hang tri gia 480.000d da duoc thanh toan thanh cong.",
-      "payload": {
-        "orderId": "uuid",
-        "subOrderId": "uuid"
-      },
-      "isRead": false,
-      "readAt": null,
-      "createdAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "notificationType": "ORDER_PAID",
+        "title": "Don hang #SUB-01 da duoc thanh toan",
+        "body": "Don hang tri gia 480.000d da duoc thanh toan thanh cong.",
+        "payload": {
+          "orderId": "uuid",
+          "subOrderId": "uuid"
+        },
+        "isRead": false,
+        "readAt": null,
+        "createdAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 10,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6206,8 +7187,14 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "updatedCount": 1,
-  "unreadCount": 2
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "updatedCount": 1,
+    "unreadCount": 2
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6236,17 +7223,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "id": "uuid",
-  "code": "EMAIL",
-  "name": "Email Service",
-  "provider": "SMTP",
-  "config": {
-    "host": "smtp.example.com",
-    "port": 587,
-    "fromAddress": "noreply@shop.example.com"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "id": "uuid",
+    "code": "EMAIL",
+    "name": "Email Service",
+    "provider": "SMTP",
+    "config": {
+      "host": "smtp.example.com",
+      "port": 587,
+      "fromAddress": "noreply@shop.example.com"
+    },
+    "isEnabled": true,
+    "updatedAt": "2026-10-26T00:00:00Z"
   },
-  "isEnabled": true,
-  "updatedAt": "2026-10-26T00:00:00Z"
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6307,19 +7300,33 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "items": [
-    {
-      "id": "uuid",
-      "code": "ORDER_PAID_EMAIL",
-      "notificationType": "ORDER_PAID",
-      "channelCode": "EMAIL",
-      "subjectTemplate": "Don hang {{orderNo}} thanh toan thanh cong",
-      "bodyTemplate": "&lt;p&gt;Xin chao {{userName}}, don hang {{orderNo}} da duoc xac nhan.&lt;/p&gt;",
-      "isMandatory": true,
-      "locale": "vi-VN",
-      "isActive": true
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "code": "ORDER_PAID_EMAIL",
+        "notificationType": "ORDER_PAID",
+        "channelCode": "EMAIL",
+        "subjectTemplate": "Don hang {{orderNo}} thanh toan thanh cong",
+        "bodyTemplate": "&lt;p&gt;Xin chao {{userName}}, don hang {{orderNo}} da duoc xac nhan.&lt;/p&gt;",
+        "isMandatory": true,
+        "locale": "vi-VN",
+        "isActive": true
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6352,13 +7359,19 @@
   <si>
     <t xml:space="preserve">201 Created:
 {
-  "id": "uuid",
-  "code": "ORDER_PAID_EMAIL",
-  "notificationType": "ORDER_PAID",
-  "channelCode": "EMAIL",
-  "isMandatory": true,
-  "locale": "vi-VN",
-  "isActive": true
+  "success": true,
+  "statusCode": 201,
+  "data": {
+    "id": "uuid",
+    "code": "ORDER_PAID_EMAIL",
+    "notificationType": "ORDER_PAID",
+    "channelCode": "EMAIL",
+    "isMandatory": true,
+    "locale": "vi-VN",
+    "isActive": true
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6390,25 +7403,38 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "total": 1,
-  "items": [
-    {
-      "notificationId": "uuid",
-      "userId": "uuid",
-      "notificationType": "ORDER_PAID",
-      "status": "COMPLETED",
-      "createdAt": "2026-10-26T00:00:00Z",
-      "deliveries": [
-        {
-          "deliveryId": "uuid",
-          "channelCode": "EMAIL",
-          "destination": "u***@gmail.com",
-          "status": "SENT",
-          "attemptCount": 1
-        }
-      ]
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "notificationId": "uuid",
+        "userId": "uuid",
+        "notificationType": "ORDER_PAID",
+        "status": "COMPLETED",
+        "createdAt": "2026-10-26T00:00:00Z",
+        "deliveries": [
+          {
+            "deliveryId": "uuid",
+            "channelCode": "EMAIL",
+            "destination": "u***@gmail.com",
+            "status": "SENT",
+            "attemptCount": 1
+          }
+        ]
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6441,17 +7467,30 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "total": 1,
-  "items": [
-    {
-      "id": "uuid",
-      "eventId": "uuid",
-      "eventType": "OrderPaid",
-      "sourceService": "Commerce",
-      "actorId": "uuid",
-      "occurredAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      {
+        "id": "uuid",
+        "eventId": "uuid",
+        "eventType": "OrderPaid",
+        "sourceService": "Commerce",
+        "actorId": "uuid",
+        "occurredAt": "2026-10-26T00:00:00Z"
+      }
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 1,
+      "totalPages": 1,
+      "hasPreviousPage": false,
+      "hasNextPage": false
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6481,17 +7520,23 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "id": "uuid",
-  "eventId": "uuid",
-  "eventType": "OrderPaid",
-  "sourceService": "Commerce",
-  "actorId": "uuid",
-  "payload": {
-    "orderId": "uuid",
-    "totalAmount": 480000
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "id": "uuid",
+    "eventId": "uuid",
+    "eventType": "OrderPaid",
+    "sourceService": "Commerce",
+    "actorId": "uuid",
+    "payload": {
+      "orderId": "uuid",
+      "totalAmount": 480000
+    },
+    "occurredAt": "2026-10-26T00:00:00Z",
+    "createdAt": "2026-10-26T00:00:00Z"
   },
-  "occurredAt": "2026-10-26T00:00:00Z",
-  "createdAt": "2026-10-26T00:00:00Z"
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
@@ -6521,31 +7566,152 @@
   <si>
     <t xml:space="preserve">200 OK:
 {
-  "currentStatus": "UP",
-  "lastCheckedAt": "2026-10-26T00:00:00Z",
-  "latestLatencyMs": 5,
-  "latestQueueDepth": 0,
-  "history": [
-    {
-      "id": "uuid",
-      "brokerName": "rabbitmq",
-      "status": "UP",
-      "latencyMs": 5,
-      "queueDepth": 0,
-      "checkedAt": "2026-10-26T00:00:00Z"
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "currentStatus": "UP",
+    "lastCheckedAt": "2026-10-26T00:00:00Z",
+    "latestLatencyMs": 5,
+    "latestQueueDepth": 0,
+    "history": [
+      {
+        "id": "uuid",
+        "brokerName": "rabbitmq",
+        "status": "UP",
+        "latencyMs": 5,
+        "queueDepth": 0,
+        "checkedAt": "2026-10-26T00:00:00Z"
+      }
+    ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
+}</t>
+  </si>
+  <si>
+    <t>NOTI-16</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Thành phần / Tiêu chuẩn</t>
+  </si>
+  <si>
+    <t>HTTP Code / Type</t>
+  </si>
+  <si>
+    <t>Cấu trúc định dạng chuẩn (Standard Structure)</t>
+  </si>
+  <si>
+    <t>Mô tả &amp; Hướng dẫn ánh xạ (Gateway Mapping &amp; Usage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApiResponse&lt;T&gt;
+(Single Success Envelope)</t>
+  </si>
+  <si>
+    <t>200 OK / 201 Created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "statusCode": 200,
+  "message": null,
+  "data": {
+    // Dữ liệu payload thực tế của nghiệp vụ
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
+}</t>
+  </si>
+  <si>
+    <t>Áp dụng cho mọi API thành công trả về 1 đối tượng duy nhất hoặc thực hiện thao tác tạo mới/cập nhật. Class C# tương ứng: Nexus.Gateway.Responses.ApiResponse&lt;T&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApiResponse&lt;PagedData&lt;T&gt;&gt;
+(Paged List Success Envelope)</t>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "statusCode": 200,
+  "data": {
+    "items": [
+      // Danh sách các đối tượng bản ghi (JSON array)
+    ],
+    "pagination": {
+      "pageIndex": 1,
+      "pageSize": 20,
+      "totalCount": 100,
+      "totalPages": 5,
+      "hasPreviousPage": false,
+      "hasNextPage": true
     }
-  ]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
 }</t>
   </si>
   <si>
-    <t>NOTI-16</t>
+    <t>Áp dụng cho tất cả 39 endpoints danh sách có phân trang. Gateway tự động map trường "items" và "pagination" từ seed fixture hoặc gRPC Paged Result. Class C#: Nexus.Gateway.Responses.PagedData&lt;T&gt;.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204 No Content
+(Empty Response Body)</t>
+  </si>
+  <si>
+    <t>(Không có body - HTTP 204 Header Only)</t>
+  </si>
+  <si>
+    <t>Áp dụng cho các API xóa thành công (DELETE) hoặc xử lý mà không cần trả về nội dung (ví dụ: đánh dấu thông báo đã đọc, hủy theo dõi).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApiErrorResponse
+(RFC 9110 ProblemDetails)</t>
+  </si>
+  <si>
+    <t>400 / 401 / 403 / 404 / 409 / 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "type": "https://tools.ietf.org/html/rfc9110#section-15.5.1",
+  "title": "Bad request",
+  "status": 400,
+  "errorCode": "VAL_INVALID_INPUT",
+  "detail": "Email is already registered in the system.",
+  "errors": {
+    "email": ["Email is already registered in the system."]
+  },
+  "traceId": "00-4bf92f3577b34da6a3ce929d0e0e4736-00f067aa0ba902b7-01",
+  "timestamp": "2026-10-26T00:00:00Z"
+}</t>
+  </si>
+  <si>
+    <t>Quy chuẩn lỗi toàn hệ thống theo RFC 9110 + AGENTS.md Nguyên tắc 5: 100% tiếng Anh Sentence case (chữ thường, chỉ viết hoa chữ cái đầu câu), errorCode viết hoa SCREAMING_SNAKE_CASE. Class C#: Nexus.Gateway.Responses.ApiErrorResponse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webhook / IPN Callback
+(External Provider Standard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "RspCode": "00",
+  "Message": "Confirm success."
+}</t>
+  </si>
+  <si>
+    <t>Áp dụng đặc thù cho các webhook nhận callback từ bên thứ 3 (ví dụ VNPay IPN) tuân theo chuẩn quy định của nhà cung cấp dịch vụ thanh toán.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -6620,8 +7786,22 @@
       <sz val="14"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6715,8 +7895,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -6931,11 +8116,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7145,6 +8352,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10420,7 +11639,7 @@
         <v>6</v>
       </c>
       <c r="G65" s="27" t="s">
-        <v>7</v>
+        <v>413</v>
       </c>
       <c r="H65" s="28" t="s">
         <v>8</v>
@@ -10465,25 +11684,25 @@
         <v>79</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E66" s="31" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F66" s="31" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H66" s="32" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
@@ -10510,28 +11729,28 @@
         <v>79</v>
       </c>
       <c r="C67" s="33" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D67" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E67" s="35" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G67" s="33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H67" s="32" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="I67" s="34" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J67" s="34" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K67" s="33"/>
       <c r="L67" s="33"/>
@@ -10557,25 +11776,25 @@
         <v>79</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E68" s="31" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H68" s="32" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
@@ -10602,31 +11821,31 @@
         <v>9</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E69" s="35" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G69" s="33" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H69" s="32" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I69" s="34" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J69" s="34" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K69" s="34" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L69" s="33"/>
       <c r="M69" s="33"/>
@@ -10651,34 +11870,34 @@
         <v>79</v>
       </c>
       <c r="C70" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="F70" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="H70" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="L70" s="10" t="s">
         <v>441</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="F70" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="H70" s="32" t="s">
-        <v>446</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="J70" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="K70" s="10" t="s">
-        <v>449</v>
-      </c>
-      <c r="L70" s="10" t="s">
-        <v>440</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -10702,25 +11921,25 @@
         <v>60</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G71" s="33" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H71" s="32" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I71" s="34" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J71" s="33"/>
       <c r="K71" s="33"/>
@@ -10747,25 +11966,25 @@
         <v>84</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E72" s="31" t="s">
         <v>75</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H72" s="32" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J72" s="11"/>
       <c r="K72" s="11"/>
@@ -10792,25 +12011,25 @@
         <v>84</v>
       </c>
       <c r="C73" s="33" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E73" s="35" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G73" s="33" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H73" s="32" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I73" s="34" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J73" s="33"/>
       <c r="K73" s="33"/>
@@ -10837,28 +12056,28 @@
         <v>79</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H74" s="32" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K74" s="11"/>
       <c r="L74" s="11"/>
@@ -10884,31 +12103,31 @@
         <v>9</v>
       </c>
       <c r="C75" s="33" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G75" s="33" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H75" s="32" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I75" s="34" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J75" s="34" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K75" s="34" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L75" s="36"/>
       <c r="M75" s="33"/>
@@ -10933,43 +12152,43 @@
         <v>9</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="H76" s="32" t="s">
+        <v>485</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="L76" s="38" t="s">
         <v>479</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="G76" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="H76" s="32" t="s">
-        <v>484</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="K76" s="37" t="s">
-        <v>470</v>
-      </c>
-      <c r="L76" s="38" t="s">
-        <v>478</v>
-      </c>
       <c r="M76" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N76" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O76" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P76" s="11"/>
       <c r="Q76" s="5"/>
@@ -10990,31 +12209,31 @@
         <v>79</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H77" s="32" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I77" s="34" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J77" s="34" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K77" s="34" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L77" s="33"/>
       <c r="M77" s="33"/>
@@ -11039,25 +12258,25 @@
         <v>79</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H78" s="32" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
@@ -11084,28 +12303,28 @@
         <v>9</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F79" s="33" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G79" s="33" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H79" s="32" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I79" s="39" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J79" s="34" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K79" s="33"/>
       <c r="L79" s="33"/>
@@ -11131,44 +12350,44 @@
         <v>9</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H80" s="40" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I80" s="41"/>
       <c r="J80" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K80" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L80" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O80" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P80" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q80" s="5"/>
       <c r="R80" s="5"/>
@@ -11186,37 +12405,37 @@
       <c r="A81" s="33"/>
       <c r="B81" s="33"/>
       <c r="C81" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D81" s="33" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F81" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G81" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H81" s="32" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I81" s="42" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J81" s="34" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K81" s="34" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L81" s="34" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M81" s="34" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N81" s="33"/>
       <c r="O81" s="33"/>
@@ -11239,37 +12458,37 @@
         <v>9</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H82" s="32" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J82" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K82" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N82" s="11"/>
       <c r="O82" s="11"/>
@@ -11292,43 +12511,43 @@
         <v>9</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F83" s="33" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G83" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H83" s="32" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I83" s="34" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J83" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K83" s="34" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L83" s="34" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M83" s="43" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O83" s="34" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P83" s="33"/>
       <c r="Q83" s="5"/>
@@ -11347,37 +12566,37 @@
       <c r="A84" s="11"/>
       <c r="B84" s="11"/>
       <c r="C84" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H84" s="32" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L84" s="10" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M84" s="10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N84" s="11"/>
       <c r="O84" s="11"/>
@@ -11400,25 +12619,25 @@
         <v>79</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F85" s="33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G85" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H85" s="32" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I85" s="34" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J85" s="33"/>
       <c r="K85" s="33"/>
@@ -11445,31 +12664,31 @@
         <v>79</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H86" s="32" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K86" s="10" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L86" s="11"/>
       <c r="M86" s="11"/>
@@ -11494,26 +12713,26 @@
         <v>79</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D87" s="33" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F87" s="33" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G87" s="33" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H87" s="32" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="I87" s="33"/>
       <c r="J87" s="33" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K87" s="33"/>
       <c r="L87" s="33"/>
@@ -11539,25 +12758,25 @@
         <v>79</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H88" s="32" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
@@ -11584,25 +12803,25 @@
         <v>79</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D89" s="33" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G89" s="33" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H89" s="32" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I89" s="34" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J89" s="33"/>
       <c r="K89" s="33"/>
@@ -11629,25 +12848,25 @@
         <v>60</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H90" s="32" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -11674,34 +12893,34 @@
         <v>9</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D91" s="33" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F91" s="33" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G91" s="33" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H91" s="32" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I91" s="42" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J91" s="34" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K91" s="34" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L91" s="34" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M91" s="33"/>
       <c r="N91" s="33"/>
@@ -11725,34 +12944,34 @@
         <v>9</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H92" s="32" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J92" s="44" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K92" s="44" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M92" s="11"/>
       <c r="N92" s="11"/>
@@ -11776,34 +12995,34 @@
         <v>60</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F93" s="33" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G93" s="33" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H93" s="32" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I93" s="42" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J93" s="34" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K93" s="34" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L93" s="34" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M93" s="33"/>
       <c r="N93" s="33"/>
@@ -11827,34 +13046,34 @@
         <v>60</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H94" s="32" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J94" s="44" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K94" s="44" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L94" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M94" s="11"/>
       <c r="N94" s="11"/>
@@ -11907,37 +13126,37 @@
         <v>9</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H96" s="32" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K96" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L96" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N96" s="11"/>
       <c r="O96" s="11"/>
@@ -11960,40 +13179,40 @@
         <v>9</v>
       </c>
       <c r="C97" s="33" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D97" s="33" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F97" s="33" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G97" s="33" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H97" s="32" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I97" s="34" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J97" s="33" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K97" s="34" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L97" s="43" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M97" s="34" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N97" s="33" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O97" s="33"/>
       <c r="P97" s="33"/>
@@ -12015,46 +13234,46 @@
         <v>9</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="J98" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K98" s="10" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L98" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N98" s="11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O98" s="11" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P98" s="11" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Q98" s="5"/>
       <c r="R98" s="5"/>
@@ -12070,7 +13289,7 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B99" s="23"/>
       <c r="C99" s="23"/>
@@ -12119,7 +13338,7 @@
         <v>6</v>
       </c>
       <c r="G100" s="47" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H100" s="28" t="s">
         <v>8</v>
@@ -12164,28 +13383,28 @@
         <v>79</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H101" s="32" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J101" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K101" s="11"/>
       <c r="L101" s="11"/>
@@ -12211,28 +13430,28 @@
         <v>79</v>
       </c>
       <c r="C102" s="49" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E102" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F102" s="51" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G102" s="51" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H102" s="32" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I102" s="50" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J102" s="50" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K102" s="49"/>
       <c r="L102" s="49"/>
@@ -12258,28 +13477,28 @@
         <v>79</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H103" s="32" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K103" s="11"/>
       <c r="L103" s="11"/>
@@ -12305,28 +13524,28 @@
         <v>9</v>
       </c>
       <c r="C104" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E104" s="51" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F104" s="51" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G104" s="51" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H104" s="32" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I104" s="50" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J104" s="50" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="K104" s="49"/>
       <c r="L104" s="49"/>
@@ -12352,28 +13571,28 @@
         <v>60</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H105" s="32" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J105" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K105" s="11"/>
       <c r="L105" s="11"/>
@@ -12399,25 +13618,25 @@
         <v>84</v>
       </c>
       <c r="C106" s="49" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E106" s="51" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F106" s="51" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G106" s="51" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H106" s="32" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I106" s="50" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J106" s="49"/>
       <c r="K106" s="49"/>
@@ -12444,25 +13663,25 @@
         <v>9</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H107" s="32" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="J107" s="11"/>
       <c r="K107" s="11"/>
@@ -12489,25 +13708,25 @@
         <v>79</v>
       </c>
       <c r="C108" s="49" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E108" s="51" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F108" s="51" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G108" s="51" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H108" s="32" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I108" s="50" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="J108" s="49"/>
       <c r="K108" s="49"/>
@@ -12534,25 +13753,25 @@
         <v>84</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H109" s="32" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J109" s="11"/>
       <c r="K109" s="11"/>
@@ -12579,25 +13798,25 @@
         <v>79</v>
       </c>
       <c r="C110" s="49" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E110" s="51" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F110" s="51" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="G110" s="51" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H110" s="32" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="I110" s="50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J110" s="49"/>
       <c r="K110" s="49"/>
@@ -12624,25 +13843,25 @@
         <v>79</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H111" s="32" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J111" s="11"/>
       <c r="K111" s="11"/>
@@ -12669,25 +13888,25 @@
         <v>60</v>
       </c>
       <c r="C112" s="49" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E112" s="51" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F112" s="51" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G112" s="51" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H112" s="32" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I112" s="50" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="J112" s="49"/>
       <c r="K112" s="49"/>
@@ -12714,28 +13933,28 @@
         <v>9</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H113" s="32" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K113" s="11"/>
       <c r="L113" s="11"/>
@@ -12761,25 +13980,25 @@
         <v>9</v>
       </c>
       <c r="C114" s="49" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E114" s="51" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F114" s="51" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G114" s="51" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H114" s="32" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I114" s="50" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J114" s="49"/>
       <c r="K114" s="49"/>
@@ -12806,25 +14025,25 @@
         <v>84</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H115" s="32" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="J115" s="11"/>
       <c r="K115" s="11"/>
@@ -12851,28 +14070,28 @@
         <v>60</v>
       </c>
       <c r="C116" s="49" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E116" s="51" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F116" s="51" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G116" s="51" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H116" s="32" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="I116" s="50" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J116" s="50" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K116" s="49"/>
       <c r="L116" s="49"/>
@@ -12898,28 +14117,28 @@
         <v>79</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H117" s="32" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
@@ -12945,28 +14164,28 @@
         <v>9</v>
       </c>
       <c r="C118" s="49" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E118" s="51" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F118" s="51" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G118" s="51" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H118" s="32" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="I118" s="50" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J118" s="50" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K118" s="49"/>
       <c r="L118" s="49"/>
@@ -12992,25 +14211,25 @@
         <v>79</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H119" s="32" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J119" s="11"/>
       <c r="K119" s="11"/>
@@ -13037,25 +14256,25 @@
         <v>9</v>
       </c>
       <c r="C120" s="49" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E120" s="51" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F120" s="51" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G120" s="51" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H120" s="32" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I120" s="50" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J120" s="49"/>
       <c r="K120" s="49"/>
@@ -13082,25 +14301,25 @@
         <v>52</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G121" s="11" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H121" s="32" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J121" s="11"/>
       <c r="K121" s="11"/>
@@ -13127,25 +14346,25 @@
         <v>84</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E122" s="51" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F122" s="51" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G122" s="51" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H122" s="32" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I122" s="50" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J122" s="49"/>
       <c r="K122" s="49"/>
@@ -13172,25 +14391,25 @@
         <v>79</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H123" s="32" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="I123" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="J123" s="11"/>
       <c r="K123" s="11"/>
@@ -13214,31 +14433,31 @@
     <row r="124" ht="409.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="49"/>
       <c r="B124" s="50" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C124" s="49" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E124" s="51" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F124" s="51" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G124" s="51" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H124" s="32" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I124" s="50" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="J124" s="50" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="K124" s="49"/>
       <c r="L124" s="49"/>
@@ -13264,28 +14483,28 @@
         <v>79</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H125" s="32" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I125" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="K125" s="11"/>
       <c r="L125" s="11"/>
@@ -13311,28 +14530,28 @@
         <v>79</v>
       </c>
       <c r="C126" s="49" t="s">
+        <v>803</v>
+      </c>
+      <c r="D126" s="49" t="s">
+        <v>804</v>
+      </c>
+      <c r="E126" s="51" t="s">
+        <v>805</v>
+      </c>
+      <c r="F126" s="51" t="s">
+        <v>665</v>
+      </c>
+      <c r="G126" s="51" t="s">
+        <v>806</v>
+      </c>
+      <c r="H126" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="I126" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="J126" s="50" t="s">
         <v>802</v>
-      </c>
-      <c r="D126" s="49" t="s">
-        <v>803</v>
-      </c>
-      <c r="E126" s="51" t="s">
-        <v>804</v>
-      </c>
-      <c r="F126" s="51" t="s">
-        <v>664</v>
-      </c>
-      <c r="G126" s="51" t="s">
-        <v>805</v>
-      </c>
-      <c r="H126" s="32" t="s">
-        <v>418</v>
-      </c>
-      <c r="I126" s="50" t="s">
-        <v>418</v>
-      </c>
-      <c r="J126" s="50" t="s">
-        <v>801</v>
       </c>
       <c r="K126" s="49"/>
       <c r="L126" s="49"/>
@@ -13358,28 +14577,28 @@
         <v>79</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H127" s="32" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="K127" s="11"/>
       <c r="L127" s="11"/>
@@ -13401,7 +14620,7 @@
     </row>
     <row r="128" ht="19.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="52" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B128" s="23"/>
       <c r="C128" s="23"/>
@@ -13450,7 +14669,7 @@
         <v>6</v>
       </c>
       <c r="G129" s="55" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H129" s="28" t="s">
         <v>8</v>
@@ -13495,28 +14714,28 @@
         <v>79</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G130" s="11" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H130" s="32" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I130" s="11" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="K130" s="11"/>
       <c r="L130" s="11"/>
@@ -13542,28 +14761,28 @@
         <v>79</v>
       </c>
       <c r="C131" s="57" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D131" s="57" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E131" s="57" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F131" s="57" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G131" s="57" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H131" s="32" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I131" s="57" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="J131" s="57" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K131" s="57"/>
       <c r="L131" s="58"/>
@@ -13589,31 +14808,31 @@
         <v>9</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G132" s="11" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H132" s="32" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I132" s="11" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="J132" s="59" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K132" s="11" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L132" s="11"/>
       <c r="M132" s="11"/>
@@ -13638,25 +14857,25 @@
         <v>52</v>
       </c>
       <c r="C133" s="57" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D133" s="57" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E133" s="57" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F133" s="57" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G133" s="57" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H133" s="32" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I133" s="57" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="J133" s="57"/>
       <c r="K133" s="57"/>
@@ -13683,25 +14902,25 @@
         <v>9</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G134" s="11" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H134" s="32" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I134" s="11" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="J134" s="11"/>
       <c r="K134" s="11"/>
@@ -13728,31 +14947,31 @@
         <v>9</v>
       </c>
       <c r="C135" s="57" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D135" s="57" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E135" s="57" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F135" s="57" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G135" s="57" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H135" s="32" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="I135" s="57" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="J135" s="60" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K135" s="57" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="L135" s="58"/>
       <c r="M135" s="58"/>
@@ -13777,25 +14996,25 @@
         <v>79</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G136" s="11" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H136" s="32" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I136" s="11" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J136" s="11"/>
       <c r="K136" s="11"/>
@@ -13822,28 +15041,28 @@
         <v>79</v>
       </c>
       <c r="C137" s="57" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D137" s="57" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E137" s="57" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F137" s="57" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G137" s="57" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H137" s="32" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="I137" s="57" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J137" s="57" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K137" s="57"/>
       <c r="L137" s="58"/>
@@ -13869,28 +15088,28 @@
         <v>9</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G138" s="11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H138" s="32" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="I138" s="11" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="J138" s="11" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="K138" s="11"/>
       <c r="L138" s="11"/>
@@ -13916,25 +15135,25 @@
         <v>79</v>
       </c>
       <c r="C139" s="57" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D139" s="57" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E139" s="57" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F139" s="57" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G139" s="57" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H139" s="32" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="I139" s="57" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J139" s="57"/>
       <c r="K139" s="57"/>
@@ -13961,28 +15180,28 @@
         <v>79</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E140" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G140" s="11" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H140" s="32" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="I140" s="11" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J140" s="59" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="K140" s="11"/>
       <c r="L140" s="11"/>
@@ -14008,25 +15227,25 @@
         <v>52</v>
       </c>
       <c r="C141" s="57" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D141" s="57" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E141" s="57" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="F141" s="57" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="G141" s="57" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H141" s="32" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I141" s="57" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="J141" s="57"/>
       <c r="K141" s="57"/>
@@ -14053,31 +15272,31 @@
         <v>9</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H142" s="32" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I142" s="11" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J142" s="59" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L142" s="11"/>
       <c r="M142" s="11"/>
@@ -14102,28 +15321,28 @@
         <v>79</v>
       </c>
       <c r="C143" s="57" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D143" s="57" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="E143" s="57" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F143" s="57" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G143" s="57" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H143" s="32" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I143" s="57" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J143" s="60" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K143" s="57"/>
       <c r="L143" s="58"/>
@@ -14149,28 +15368,28 @@
         <v>79</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H144" s="32" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I144" s="11" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J144" s="11" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K144" s="11"/>
       <c r="L144" s="11"/>
@@ -14196,25 +15415,25 @@
         <v>79</v>
       </c>
       <c r="C145" s="57" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D145" s="57" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E145" s="57" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F145" s="57" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="G145" s="57" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H145" s="32" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="I145" s="57" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J145" s="57"/>
       <c r="K145" s="57"/>
@@ -14238,28 +15457,28 @@
     <row r="146" ht="153.75" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="11"/>
       <c r="B146" s="11" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H146" s="32" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I146" s="11" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J146" s="11"/>
       <c r="K146" s="11"/>
@@ -14286,25 +15505,25 @@
         <v>79</v>
       </c>
       <c r="C147" s="57" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D147" s="57" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E147" s="57" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F147" s="57" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G147" s="57" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H147" s="32" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I147" s="57" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="J147" s="58"/>
       <c r="K147" s="58"/>
@@ -14331,25 +15550,25 @@
         <v>79</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="G148" s="11" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H148" s="32" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I148" s="11" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="J148" s="11"/>
       <c r="K148" s="11"/>
@@ -15126,7 +16345,7 @@
     </row>
     <row r="175" ht="16.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="61" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B175" s="23"/>
       <c r="C175" s="23"/>
@@ -15175,7 +16394,7 @@
         <v>6</v>
       </c>
       <c r="G176" s="65" t="s">
-        <v>7</v>
+        <v>413</v>
       </c>
       <c r="H176" s="28" t="s">
         <v>8</v>
@@ -15220,25 +16439,25 @@
         <v>79</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D177" s="11" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E177" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G177" s="11" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H177" s="40" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="I177" s="68" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J177" s="11"/>
       <c r="K177" s="11"/>
@@ -15265,25 +16484,25 @@
         <v>9</v>
       </c>
       <c r="C178" s="70" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D178" s="70" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E178" s="70" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F178" s="70" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G178" s="70" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H178" s="40" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="I178" s="71" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J178" s="70"/>
       <c r="K178" s="70"/>
@@ -15310,25 +16529,25 @@
         <v>9</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G179" s="11" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H179" s="40" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I179" s="68" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J179" s="11"/>
       <c r="K179" s="11"/>
@@ -15355,25 +16574,25 @@
         <v>9</v>
       </c>
       <c r="C180" s="70" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D180" s="70" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E180" s="70" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F180" s="70" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G180" s="70" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H180" s="40" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I180" s="71" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J180" s="70"/>
       <c r="K180" s="70"/>
@@ -15400,25 +16619,25 @@
         <v>9</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E181" s="11" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G181" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H181" s="40" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="I181" s="68" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J181" s="11"/>
       <c r="K181" s="11"/>
@@ -15445,25 +16664,25 @@
         <v>60</v>
       </c>
       <c r="C182" s="70" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D182" s="70" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="E182" s="70" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F182" s="70" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G182" s="70" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H182" s="40" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="I182" s="71" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J182" s="70"/>
       <c r="K182" s="70"/>
@@ -15490,25 +16709,25 @@
         <v>79</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E183" s="11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F183" s="11" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G183" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H183" s="40" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I183" s="72" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -15535,25 +16754,25 @@
         <v>9</v>
       </c>
       <c r="C184" s="70" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D184" s="70" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E184" s="70" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F184" s="70" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G184" s="70" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H184" s="40" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="I184" s="73" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="J184" s="70"/>
       <c r="K184" s="70"/>
@@ -15580,22 +16799,22 @@
         <v>9</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D185" s="11" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E185" s="11" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F185" s="11" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G185" s="11" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H185" s="32" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="I185" s="11"/>
       <c r="J185" s="11"/>
@@ -15623,22 +16842,22 @@
         <v>84</v>
       </c>
       <c r="C186" s="70" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D186" s="70" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E186" s="70" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F186" s="70" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G186" s="70" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H186" s="32" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="I186" s="70"/>
       <c r="J186" s="70"/>
@@ -15666,22 +16885,22 @@
         <v>79</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D187" s="11" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E187" s="11" t="s">
         <v>75</v>
       </c>
       <c r="F187" s="11" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G187" s="11" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H187" s="32" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="I187" s="11"/>
       <c r="J187" s="11"/>
@@ -15709,22 +16928,22 @@
         <v>52</v>
       </c>
       <c r="C188" s="70" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D188" s="70" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E188" s="70" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F188" s="70" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G188" s="70" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H188" s="32" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="I188" s="70"/>
       <c r="J188" s="70"/>
@@ -15752,22 +16971,22 @@
         <v>79</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="E189" s="11" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F189" s="11" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="G189" s="11" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H189" s="32" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I189" s="11"/>
       <c r="J189" s="11"/>
@@ -15795,22 +17014,22 @@
         <v>60</v>
       </c>
       <c r="C190" s="70" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D190" s="70" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E190" s="70" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F190" s="70" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G190" s="70" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H190" s="32" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="I190" s="70"/>
       <c r="J190" s="70"/>
@@ -15838,22 +17057,22 @@
         <v>79</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D191" s="11" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E191" s="11" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F191" s="11" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G191" s="11" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H191" s="32" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="I191" s="11"/>
       <c r="J191" s="11"/>
@@ -15881,22 +17100,22 @@
         <v>52</v>
       </c>
       <c r="C192" s="70" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D192" s="70" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E192" s="70" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F192" s="70" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G192" s="70" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H192" s="32" t="s">
         <v>1015</v>
-      </c>
-      <c r="E192" s="70" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F192" s="70" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G192" s="70" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H192" s="32" t="s">
-        <v>1014</v>
       </c>
       <c r="I192" s="70"/>
       <c r="J192" s="70"/>
@@ -15924,22 +17143,22 @@
         <v>79</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D193" s="11" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E193" s="11" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F193" s="11" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G193" s="11" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H193" s="32" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="I193" s="11"/>
       <c r="J193" s="11"/>
@@ -15967,22 +17186,22 @@
         <v>9</v>
       </c>
       <c r="C194" s="70" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D194" s="70" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E194" s="70" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F194" s="70" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G194" s="70" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H194" s="32" t="s">
         <v>1024</v>
-      </c>
-      <c r="E194" s="70" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F194" s="70" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G194" s="70" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H194" s="32" t="s">
-        <v>1023</v>
       </c>
       <c r="I194" s="70"/>
       <c r="J194" s="70"/>
@@ -16010,22 +17229,22 @@
         <v>79</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D195" s="11" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E195" s="11" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F195" s="11" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G195" s="11" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H195" s="32" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="I195" s="11"/>
       <c r="J195" s="11"/>
@@ -16053,22 +17272,22 @@
         <v>79</v>
       </c>
       <c r="C196" s="70" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D196" s="70" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E196" s="70" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F196" s="70" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G196" s="70" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H196" s="32" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="I196" s="70"/>
       <c r="J196" s="70"/>
@@ -16096,22 +17315,22 @@
         <v>79</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E197" s="11" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F197" s="11" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G197" s="11" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H197" s="32" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="I197" s="11"/>
       <c r="J197" s="11"/>
@@ -16139,22 +17358,22 @@
         <v>79</v>
       </c>
       <c r="C198" s="70" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D198" s="70" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E198" s="70" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F198" s="70" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="G198" s="70" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H198" s="32" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="I198" s="70"/>
       <c r="J198" s="70"/>
@@ -39967,4 +41186,124 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D1" s="74" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="75">
+        <v>1</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D2" s="77" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="3" ht="140" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="75">
+        <v>2</v>
+      </c>
+      <c r="B3" s="76" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E3" s="76" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="75">
+        <v>3</v>
+      </c>
+      <c r="B4" s="76" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>692</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E4" s="76" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="5" ht="140" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="75">
+        <v>4</v>
+      </c>
+      <c r="B5" s="76" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E5" s="76" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="6" ht="140" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="75">
+        <v>5</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D6" s="77" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E6" s="76" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
 </file>